--- a/ALCORTA 146/Julio/Julio.xlsx
+++ b/ALCORTA 146/Julio/Julio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\ALCORTA 146\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ALCORTA 146\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4356493B-5621-4870-839F-3F3E3C2D9C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A26512E-E21D-48B7-BE4B-1B512F5FA763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,14 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$55</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Recibo '!$E$6:$N$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$125</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$126</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="205">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -368,9 +368,6 @@
     <t xml:space="preserve">Sueldo SR Vicente Aldo Adrian </t>
   </si>
   <si>
-    <t>Retenciones</t>
-  </si>
-  <si>
     <t xml:space="preserve">TOTAL </t>
   </si>
   <si>
@@ -401,18 +398,12 @@
     <t>b</t>
   </si>
   <si>
-    <t>e</t>
-  </si>
-  <si>
     <t>ARBA</t>
   </si>
   <si>
     <t xml:space="preserve">EDESUR Nro de cliente : 01121995   </t>
   </si>
   <si>
-    <t>HABERES</t>
-  </si>
-  <si>
     <t>TSG</t>
   </si>
   <si>
@@ -447,9 +438,6 @@
   </si>
   <si>
     <t>Angela</t>
-  </si>
-  <si>
-    <t>E</t>
   </si>
   <si>
     <t>HONORARIOS</t>
@@ -585,33 +573,12 @@
     <t>ESTA ES LARROCA</t>
   </si>
   <si>
-    <t>Aumentados en marz</t>
-  </si>
-  <si>
-    <t>FERNANDA</t>
-  </si>
-  <si>
     <t>RUSSO</t>
   </si>
   <si>
-    <t>Mes MAYO</t>
-  </si>
-  <si>
     <t>ARCA MES DE MAYO</t>
   </si>
   <si>
-    <t>EDESUR Nro de cliente : 01121995 - Mes de Mayo sin abonar</t>
-  </si>
-  <si>
-    <t>Cuota 6</t>
-  </si>
-  <si>
-    <t>Debito 12/06</t>
-  </si>
-  <si>
-    <t>Debito 09/06</t>
-  </si>
-  <si>
     <t xml:space="preserve">PREVISION ORDINARIA </t>
   </si>
   <si>
@@ -633,30 +600,66 @@
     <t>Sindicatos periodo JULIO</t>
   </si>
   <si>
-    <t xml:space="preserve">AYSA  - Mes de JULIO </t>
-  </si>
-  <si>
-    <t>Fumigacion -  JULIO</t>
-  </si>
-  <si>
     <t>Metrogas JULIO</t>
   </si>
   <si>
     <t>VTO 14/08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Remuneraciones sujetas a retencion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Remuneraciones excentas</t>
+  </si>
+  <si>
+    <t>Aumentados en juli</t>
+  </si>
+  <si>
+    <t>Debito 14/07</t>
+  </si>
+  <si>
+    <t>Cuota 7</t>
+  </si>
+  <si>
+    <t>AYSA  - Mes de JULIO - Vto 21/07</t>
+  </si>
+  <si>
+    <t>AYSA  - Mes de JULIO - Vto 03/07</t>
+  </si>
+  <si>
+    <t>Debito 10/07</t>
+  </si>
+  <si>
+    <t>Fumigacion mayo, junio, julio</t>
+  </si>
+  <si>
+    <t>Fernanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R DE FIORE </t>
+  </si>
+  <si>
+    <t>Deposito en cuenta bancaria</t>
+  </si>
+  <si>
+    <t>Deposito en ef</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  <numFmts count="8">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="d/m"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="d/m"/>
+    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="173" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -1456,25 +1459,25 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="8" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1482,35 +1485,34 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="6" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="4" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1520,7 +1522,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1548,19 +1550,19 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1570,72 +1572,68 @@
     <xf numFmtId="16" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1678,20 +1676,35 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1708,21 +1721,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1730,7 +1728,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="11" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="14" fillId="11" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1746,7 +1744,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2112,430 +2112,428 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M125"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M126"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="7" width="13" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="59"/>
-      <c r="B1" s="60" t="s">
-        <v>154</v>
-      </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-    </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="61"/>
-      <c r="B2" s="62" t="s">
-        <v>149</v>
-      </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="64"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="65"/>
-      <c r="B3" s="66" t="s">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="58"/>
+      <c r="B1" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+    </row>
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="63"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="64"/>
+      <c r="B3" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="65"/>
-      <c r="B4" s="66" t="s">
-        <v>178</v>
-      </c>
-      <c r="C4" s="66" t="s">
-        <v>177</v>
-      </c>
-      <c r="D4" s="66"/>
-      <c r="E4" s="67"/>
-    </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="65"/>
-      <c r="B5" s="66" t="s">
-        <v>179</v>
-      </c>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="67"/>
-    </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="68" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="69" t="s">
-        <v>198</v>
-      </c>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69" t="s">
-        <v>145</v>
-      </c>
-      <c r="E6" s="70"/>
-    </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="65"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="67"/>
-    </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="68" t="s">
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="66"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="64"/>
+      <c r="B4" s="65" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" s="65" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4" s="65"/>
+      <c r="E4" s="66"/>
+    </row>
+    <row r="5" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="64"/>
+      <c r="B5" s="65" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="66"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" s="69"/>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="64"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="66"/>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="69"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="70"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="71"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-    </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="71"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-    </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="71"/>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="71"/>
-      <c r="B12" s="71"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-    </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="71"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="71"/>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="150" t="s">
-        <v>204</v>
-      </c>
-      <c r="B15" s="150"/>
-      <c r="C15" s="150"/>
-      <c r="D15" s="150"/>
-      <c r="E15" s="150"/>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="150"/>
-      <c r="B16" s="150"/>
-      <c r="C16" s="150"/>
-      <c r="D16" s="150"/>
-      <c r="E16" s="150"/>
-    </row>
-    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="150"/>
-      <c r="B17" s="150"/>
-      <c r="C17" s="150"/>
-      <c r="D17" s="150"/>
-      <c r="E17" s="150"/>
-    </row>
-    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="150"/>
-      <c r="B18" s="150"/>
-      <c r="C18" s="150"/>
-      <c r="D18" s="150"/>
-      <c r="E18" s="150"/>
-    </row>
-    <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="71"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="71"/>
-    </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="71"/>
-      <c r="B20" s="71"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-    </row>
-    <row r="21" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="71"/>
-      <c r="B21" s="71"/>
-      <c r="C21" s="71"/>
-      <c r="D21" s="71"/>
-      <c r="E21" s="71"/>
-    </row>
-    <row r="22" spans="1:5" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="151"/>
-      <c r="B22" s="152"/>
-      <c r="C22" s="152"/>
-      <c r="D22" s="152"/>
-      <c r="E22" s="152"/>
-    </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="152"/>
-      <c r="B23" s="152"/>
-      <c r="C23" s="152"/>
-      <c r="D23" s="152"/>
-      <c r="E23" s="152"/>
-    </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="152"/>
-      <c r="B24" s="152"/>
-      <c r="C24" s="152"/>
-      <c r="D24" s="152"/>
-      <c r="E24" s="152"/>
-    </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="152"/>
-      <c r="B25" s="152"/>
-      <c r="C25" s="152"/>
-      <c r="D25" s="152"/>
-      <c r="E25" s="152"/>
-    </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="152"/>
-      <c r="B26" s="152"/>
-      <c r="C26" s="152"/>
-      <c r="D26" s="152"/>
-      <c r="E26" s="152"/>
-    </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="71"/>
-      <c r="B27" s="71"/>
-      <c r="C27" s="71"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="71"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="72" t="s">
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="69"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="70"/>
+      <c r="B9" s="70"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+    </row>
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="70"/>
+      <c r="B10" s="70"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+    </row>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="70"/>
+      <c r="B11" s="70"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="70"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+    </row>
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="70"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="70"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="147" t="s">
+        <v>191</v>
+      </c>
+      <c r="B15" s="147"/>
+      <c r="C15" s="147"/>
+      <c r="D15" s="147"/>
+      <c r="E15" s="147"/>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="147"/>
+      <c r="B16" s="147"/>
+      <c r="C16" s="147"/>
+      <c r="D16" s="147"/>
+      <c r="E16" s="147"/>
+    </row>
+    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="147"/>
+      <c r="B17" s="147"/>
+      <c r="C17" s="147"/>
+      <c r="D17" s="147"/>
+      <c r="E17" s="147"/>
+    </row>
+    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="147"/>
+      <c r="B18" s="147"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
+    </row>
+    <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="70"/>
+      <c r="B19" s="70"/>
+      <c r="C19" s="70"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+    </row>
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="70"/>
+      <c r="B20" s="70"/>
+      <c r="C20" s="70"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+    </row>
+    <row r="21" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="70"/>
+      <c r="B21" s="70"/>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+    </row>
+    <row r="22" spans="1:5" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="148"/>
+      <c r="B22" s="149"/>
+      <c r="C22" s="149"/>
+      <c r="D22" s="149"/>
+      <c r="E22" s="149"/>
+    </row>
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="149"/>
+      <c r="B23" s="149"/>
+      <c r="C23" s="149"/>
+      <c r="D23" s="149"/>
+      <c r="E23" s="149"/>
+    </row>
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="149"/>
+      <c r="B24" s="149"/>
+      <c r="C24" s="149"/>
+      <c r="D24" s="149"/>
+      <c r="E24" s="149"/>
+    </row>
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="149"/>
+      <c r="B25" s="149"/>
+      <c r="C25" s="149"/>
+      <c r="D25" s="149"/>
+      <c r="E25" s="149"/>
+    </row>
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="149"/>
+      <c r="B26" s="149"/>
+      <c r="C26" s="149"/>
+      <c r="D26" s="149"/>
+      <c r="E26" s="149"/>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="70"/>
+      <c r="B27" s="70"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="73"/>
-      <c r="C28" s="74"/>
-      <c r="D28" s="75"/>
-      <c r="E28" s="76"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B28" s="72"/>
+      <c r="C28" s="73"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="75"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B29" s="19"/>
       <c r="C29" s="19"/>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="77" t="s">
+    <row r="30" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="76" t="s">
         <v>112</v>
       </c>
-      <c r="B30" s="78" t="s">
-        <v>127</v>
-      </c>
-      <c r="C30" s="78" t="s">
-        <v>188</v>
-      </c>
-      <c r="D30" s="79">
-        <v>1612833.26</v>
-      </c>
-      <c r="E30" s="78"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="77"/>
-      <c r="B31" s="78" t="s">
-        <v>113</v>
-      </c>
-      <c r="C31" s="78"/>
-      <c r="D31" s="79">
-        <v>-350791.24</v>
-      </c>
-      <c r="E31" s="78"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="77"/>
-      <c r="B32" s="78" t="s">
-        <v>146</v>
-      </c>
-      <c r="C32" s="78"/>
-      <c r="D32" s="79">
-        <v>0.98</v>
-      </c>
-      <c r="E32" s="78"/>
-    </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="77"/>
-      <c r="B33" s="78"/>
-      <c r="C33" s="78"/>
-      <c r="D33" s="80"/>
-      <c r="E33" s="78"/>
-    </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="78"/>
-      <c r="B34" s="78"/>
-      <c r="C34" s="78"/>
-      <c r="D34" s="80"/>
-      <c r="E34" s="78"/>
-    </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="78"/>
-      <c r="B35" s="78"/>
-      <c r="C35" s="78"/>
-      <c r="D35" s="81"/>
-      <c r="E35" s="78"/>
-    </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="78"/>
-      <c r="B36" s="78"/>
-      <c r="C36" s="78"/>
-      <c r="D36" s="81"/>
-      <c r="E36" s="78"/>
-    </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="188" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="77"/>
+      <c r="D30" s="189">
+        <v>2462481.7200000002</v>
+      </c>
+      <c r="E30" s="77"/>
+    </row>
+    <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="76"/>
+      <c r="B31" s="140" t="s">
+        <v>193</v>
+      </c>
+      <c r="C31" s="77"/>
+      <c r="D31" s="189">
+        <v>7810519.0499999998</v>
+      </c>
+      <c r="E31" s="77"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="76"/>
+      <c r="B32" s="77" t="s">
+        <v>142</v>
+      </c>
+      <c r="C32" s="77"/>
+      <c r="D32" s="78">
+        <v>-535589.77</v>
+      </c>
+      <c r="E32" s="77"/>
+    </row>
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="76"/>
+      <c r="B33" s="77"/>
+      <c r="C33" s="77"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="77"/>
+    </row>
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="77"/>
+      <c r="B34" s="77"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="79"/>
+      <c r="E34" s="77"/>
+    </row>
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="77"/>
+      <c r="B35" s="77"/>
+      <c r="C35" s="77"/>
+      <c r="D35" s="80"/>
+      <c r="E35" s="77"/>
+    </row>
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="77"/>
+      <c r="B36" s="77"/>
+      <c r="C36" s="77"/>
+      <c r="D36" s="80"/>
+      <c r="E36" s="77"/>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="82"/>
-      <c r="E37" s="83">
+      <c r="B37" s="37"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="82">
         <f>SUM(D27:D34)</f>
-        <v>1262043</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="78" t="s">
-        <v>157</v>
-      </c>
-      <c r="B38" s="78"/>
-      <c r="C38" s="78"/>
-      <c r="D38" s="79"/>
-      <c r="E38" s="78"/>
+        <v>9737411</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="77" t="s">
+        <v>153</v>
+      </c>
+      <c r="B38" s="77"/>
+      <c r="C38" s="77"/>
+      <c r="D38" s="78"/>
+      <c r="E38" s="77"/>
       <c r="G38">
         <v>235611</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="78" t="s">
-        <v>156</v>
-      </c>
-      <c r="B39" s="78"/>
-      <c r="C39" s="78"/>
-      <c r="D39" s="79"/>
-      <c r="E39" s="78"/>
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="77" t="s">
+        <v>152</v>
+      </c>
+      <c r="B39" s="77"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="77"/>
       <c r="G39" s="5">
         <f>E37+E41-G38</f>
-        <v>1026432</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="78" t="s">
-        <v>146</v>
-      </c>
-      <c r="B40" s="78"/>
-      <c r="C40" s="78"/>
-      <c r="D40" s="84"/>
-      <c r="E40" s="78"/>
-    </row>
-    <row r="41" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>9501800</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="77" t="s">
+        <v>142</v>
+      </c>
+      <c r="B40" s="77"/>
+      <c r="C40" s="77"/>
+      <c r="D40" s="83"/>
+      <c r="E40" s="77"/>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="20" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B41" s="20"/>
       <c r="C41" s="20"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="83">
+      <c r="D41" s="36"/>
+      <c r="E41" s="82">
         <f>SUM(D38:D40)</f>
         <v>0</v>
       </c>
       <c r="F41" s="5"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B42" s="19"/>
       <c r="C42" s="19"/>
       <c r="D42" s="21"/>
-      <c r="E42" s="85"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="78" t="s">
-        <v>142</v>
-      </c>
-      <c r="B43" s="78" t="s">
-        <v>199</v>
-      </c>
-      <c r="C43" s="78"/>
-      <c r="D43" s="79">
-        <v>28000</v>
-      </c>
-      <c r="E43" s="86"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="78" t="s">
-        <v>143</v>
-      </c>
-      <c r="B44" s="78" t="s">
-        <v>199</v>
-      </c>
-      <c r="C44" s="78"/>
-      <c r="D44" s="79">
-        <v>112000</v>
-      </c>
-      <c r="E44" s="86"/>
+      <c r="E42" s="84"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="77" t="s">
+        <v>138</v>
+      </c>
+      <c r="B43" s="77" t="s">
+        <v>188</v>
+      </c>
+      <c r="C43" s="77"/>
+      <c r="D43" s="189">
+        <v>30000</v>
+      </c>
+      <c r="E43" s="85"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="77" t="s">
+        <v>139</v>
+      </c>
+      <c r="B44" s="77" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="77"/>
+      <c r="D44" s="189">
+        <v>123100</v>
+      </c>
+      <c r="E44" s="85"/>
       <c r="G44" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="78"/>
-      <c r="B45" s="78"/>
-      <c r="C45" s="78"/>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="77"/>
+      <c r="B45" s="77"/>
+      <c r="C45" s="77"/>
       <c r="D45" s="17"/>
-      <c r="E45" s="86"/>
-    </row>
-    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E45" s="85"/>
+    </row>
+    <row r="46" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B46" s="20"/>
       <c r="C46" s="20"/>
       <c r="D46" s="25"/>
-      <c r="E46" s="87">
+      <c r="E46" s="86">
         <f>SUM(D43:D44)</f>
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>153100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
         <v>2</v>
       </c>
@@ -2544,758 +2542,765 @@
       <c r="D47" s="22"/>
       <c r="E47" s="22"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="77" t="s">
-        <v>128</v>
-      </c>
-      <c r="B48" s="78"/>
-      <c r="C48" s="78" t="s">
-        <v>191</v>
-      </c>
-      <c r="D48" s="17">
-        <v>25842</v>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="76" t="s">
+        <v>125</v>
+      </c>
+      <c r="B48" s="77"/>
+      <c r="C48" s="77" t="s">
+        <v>196</v>
+      </c>
+      <c r="D48" s="145">
+        <v>28208</v>
       </c>
       <c r="E48" s="24"/>
     </row>
-    <row r="49" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="77"/>
-      <c r="B49" s="78"/>
-      <c r="C49" s="78"/>
+    <row r="49" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="76"/>
+      <c r="B49" s="77"/>
+      <c r="C49" s="77"/>
       <c r="D49" s="17"/>
-      <c r="E49" s="88"/>
-    </row>
-    <row r="50" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E49" s="87"/>
+    </row>
+    <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="20" t="s">
         <v>3</v>
       </c>
       <c r="B50" s="20"/>
       <c r="C50" s="20"/>
       <c r="D50" s="25"/>
-      <c r="E50" s="89">
+      <c r="E50" s="88">
         <f>SUM(D48)</f>
-        <v>25842</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+        <v>28208</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="B51" s="38"/>
-      <c r="C51" s="38"/>
+        <v>114</v>
+      </c>
+      <c r="B51" s="37"/>
+      <c r="C51" s="37"/>
       <c r="D51" s="26"/>
-      <c r="E51" s="90"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="78" t="s">
+      <c r="E51" s="89"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="77" t="s">
+        <v>182</v>
+      </c>
+      <c r="B52" s="77"/>
+      <c r="C52" s="77" t="s">
+        <v>199</v>
+      </c>
+      <c r="D52" s="145">
+        <v>1147893.6299999999</v>
+      </c>
+      <c r="E52" s="24"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="77" t="s">
         <v>189</v>
       </c>
-      <c r="B52" s="78"/>
-      <c r="C52" s="78" t="s">
-        <v>193</v>
-      </c>
-      <c r="D52" s="191">
-        <v>1147893.6299999999</v>
-      </c>
-      <c r="E52" s="24"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="78" t="s">
-        <v>200</v>
-      </c>
-      <c r="B53" s="78" t="s">
-        <v>131</v>
-      </c>
-      <c r="C53" s="78" t="s">
-        <v>192</v>
-      </c>
-      <c r="D53" s="140">
+      <c r="B53" s="77" t="s">
+        <v>128</v>
+      </c>
+      <c r="C53" s="77" t="s">
+        <v>195</v>
+      </c>
+      <c r="D53" s="139">
         <v>110811.68</v>
       </c>
       <c r="E53" s="24"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="78" t="str">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="77" t="str">
         <f>A53</f>
         <v>Sindicatos periodo JULIO</v>
       </c>
-      <c r="B54" s="78" t="s">
-        <v>129</v>
-      </c>
-      <c r="C54" s="78" t="str">
+      <c r="B54" s="77" t="s">
+        <v>126</v>
+      </c>
+      <c r="C54" s="77" t="str">
         <f>C53</f>
-        <v>Debito 12/06</v>
-      </c>
-      <c r="D54" s="191">
+        <v>Debito 14/07</v>
+      </c>
+      <c r="D54" s="145">
         <v>196457.31</v>
       </c>
       <c r="E54" s="24"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="78" t="str">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="77" t="str">
         <f>A54</f>
         <v>Sindicatos periodo JULIO</v>
       </c>
-      <c r="B55" s="78" t="s">
-        <v>130</v>
-      </c>
-      <c r="C55" s="78" t="str">
+      <c r="B55" s="77" t="s">
+        <v>127</v>
+      </c>
+      <c r="C55" s="77" t="str">
         <f>C54</f>
-        <v>Debito 12/06</v>
-      </c>
-      <c r="D55" s="191">
+        <v>Debito 14/07</v>
+      </c>
+      <c r="D55" s="145">
         <v>12312.41</v>
       </c>
-      <c r="E55" s="88"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="78"/>
-      <c r="B56" s="78"/>
-      <c r="C56" s="78"/>
+      <c r="E55" s="87"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="77"/>
+      <c r="B56" s="77"/>
+      <c r="C56" s="77"/>
       <c r="D56" s="17"/>
       <c r="E56" s="24"/>
     </row>
-    <row r="57" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B57" s="38"/>
-      <c r="C57" s="38"/>
+      <c r="B57" s="37"/>
+      <c r="C57" s="37"/>
       <c r="D57" s="27"/>
-      <c r="E57" s="91">
+      <c r="E57" s="90">
         <f>SUM(D52:D56)</f>
         <v>1467475.0299999998</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="B58" s="38"/>
-      <c r="C58" s="38"/>
+        <v>116</v>
+      </c>
+      <c r="B58" s="37"/>
+      <c r="C58" s="37"/>
       <c r="D58" s="26"/>
-      <c r="E58" s="90"/>
-    </row>
-    <row r="59" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="78" t="s">
-        <v>201</v>
-      </c>
-      <c r="B59" s="92"/>
-      <c r="C59" s="78"/>
-      <c r="D59" s="191">
+      <c r="E58" s="89"/>
+    </row>
+    <row r="59" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="77" t="s">
+        <v>198</v>
+      </c>
+      <c r="B59" s="91"/>
+      <c r="C59" s="77"/>
+      <c r="D59" s="145">
         <v>477093.49</v>
       </c>
       <c r="E59" s="24"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="92" t="s">
-        <v>180</v>
-      </c>
-      <c r="B60" s="92"/>
-      <c r="C60" s="78"/>
-      <c r="D60" s="191">
+    <row r="60" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="77" t="s">
+        <v>197</v>
+      </c>
+      <c r="B60" s="91"/>
+      <c r="C60" s="77"/>
+      <c r="D60" s="145">
+        <v>486867.96</v>
+      </c>
+      <c r="E60" s="24"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="91" t="s">
+        <v>176</v>
+      </c>
+      <c r="B61" s="91"/>
+      <c r="C61" s="77"/>
+      <c r="D61" s="145">
         <v>59700</v>
       </c>
-      <c r="E60" s="17"/>
-    </row>
-    <row r="61" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="78" t="s">
-        <v>125</v>
-      </c>
-      <c r="B61" s="93"/>
-      <c r="C61" s="94"/>
-      <c r="D61" s="17">
-        <v>0</v>
-      </c>
-      <c r="E61" s="24"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="78" t="s">
-        <v>202</v>
-      </c>
-      <c r="B62" s="78"/>
-      <c r="C62" s="94"/>
+      <c r="E61" s="17"/>
+    </row>
+    <row r="62" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="77" t="s">
+        <v>123</v>
+      </c>
+      <c r="B62" s="92"/>
+      <c r="C62" s="93"/>
       <c r="D62" s="17">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="E62" s="24"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="78" t="s">
-        <v>151</v>
-      </c>
-      <c r="B63" s="78"/>
-      <c r="C63" s="78"/>
-      <c r="D63" s="191">
-        <v>20912.349999999999</v>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="77" t="s">
+        <v>200</v>
+      </c>
+      <c r="B63" s="77"/>
+      <c r="C63" s="93"/>
+      <c r="D63" s="145">
+        <v>115000</v>
       </c>
       <c r="E63" s="24"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="78" t="s">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="77" t="s">
+        <v>147</v>
+      </c>
+      <c r="B64" s="77"/>
+      <c r="C64" s="142"/>
+      <c r="D64" s="142">
+        <v>203720.4</v>
+      </c>
+      <c r="E64" s="24"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="77" t="s">
+        <v>118</v>
+      </c>
+      <c r="B65" s="77"/>
+      <c r="C65" s="145"/>
+      <c r="D65" s="145">
+        <v>180608.79</v>
+      </c>
+      <c r="E65" s="24"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="77" t="s">
+        <v>124</v>
+      </c>
+      <c r="B66" s="77"/>
+      <c r="C66" s="145"/>
+      <c r="D66" s="145">
+        <v>5931.42</v>
+      </c>
+      <c r="E66" s="142"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="77" t="s">
         <v>190</v>
       </c>
-      <c r="B64" s="78"/>
-      <c r="C64" s="78"/>
-      <c r="D64" s="191">
-        <v>180608.79</v>
-      </c>
-      <c r="E64" s="24"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="78" t="s">
-        <v>119</v>
-      </c>
-      <c r="B65" s="78"/>
-      <c r="C65" s="78"/>
-      <c r="D65" s="191">
-        <v>5931.42</v>
-      </c>
-      <c r="E65" s="24"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="78" t="s">
-        <v>126</v>
-      </c>
-      <c r="B66" s="78"/>
-      <c r="C66" s="78"/>
-      <c r="D66" s="145">
-        <v>101821.18</v>
-      </c>
-      <c r="E66" s="143"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="78" t="s">
-        <v>203</v>
-      </c>
-      <c r="B67" s="78"/>
-      <c r="C67" s="78"/>
-      <c r="D67" s="17">
-        <v>16245.66</v>
-      </c>
+      <c r="B67" s="77"/>
+      <c r="C67" s="77"/>
+      <c r="D67" s="17"/>
       <c r="E67" s="24"/>
     </row>
-    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="78"/>
-      <c r="B68" s="95"/>
-      <c r="C68" s="96"/>
+    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="77"/>
+      <c r="B68" s="94"/>
+      <c r="C68" s="95"/>
       <c r="D68" s="17"/>
-      <c r="E68" s="88"/>
-    </row>
-    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E68" s="87"/>
+    </row>
+    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="20" t="s">
         <v>5</v>
       </c>
       <c r="B69" s="20"/>
       <c r="C69" s="20"/>
       <c r="D69" s="25"/>
-      <c r="E69" s="89">
+      <c r="E69" s="88">
         <f>SUM(D59:D68)</f>
-        <v>917312.89</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1528922.0599999998</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
       <c r="D70" s="25"/>
-      <c r="E70" s="89"/>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="78" t="s">
-        <v>162</v>
-      </c>
-      <c r="B71" s="78"/>
-      <c r="C71" s="78"/>
-      <c r="D71" s="17">
-        <v>44595</v>
-      </c>
-      <c r="E71" s="86"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="78" t="s">
-        <v>181</v>
-      </c>
-      <c r="B72" s="78"/>
-      <c r="C72" s="78"/>
+      <c r="E70" s="88"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="77" t="s">
+        <v>158</v>
+      </c>
+      <c r="B71" s="77"/>
+      <c r="C71" s="77"/>
+      <c r="D71" s="145">
+        <v>49294.58</v>
+      </c>
+      <c r="E71" s="85"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="77" t="s">
+        <v>177</v>
+      </c>
+      <c r="B72" s="77"/>
+      <c r="C72" s="77"/>
       <c r="D72" s="17">
         <v>52084.53</v>
       </c>
       <c r="E72" s="24"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="78" t="s">
-        <v>150</v>
-      </c>
-      <c r="B73" s="78"/>
-      <c r="C73" s="78"/>
-      <c r="D73" s="24">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="77" t="s">
+        <v>146</v>
+      </c>
+      <c r="B73" s="77"/>
+      <c r="C73" s="77"/>
+      <c r="D73" s="139">
         <v>2350</v>
       </c>
       <c r="E73" s="24"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="78"/>
-      <c r="B74" s="78"/>
-      <c r="C74" s="78"/>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="77"/>
+      <c r="B74" s="77"/>
+      <c r="C74" s="77"/>
       <c r="D74" s="24"/>
       <c r="E74" s="17"/>
     </row>
-    <row r="75" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="20" t="s">
         <v>16</v>
       </c>
       <c r="B75" s="19"/>
       <c r="C75" s="19"/>
       <c r="D75" s="19"/>
-      <c r="E75" s="97">
+      <c r="E75" s="96">
         <f>SUM(D71:D74)</f>
-        <v>99029.53</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>103729.11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="19" t="s">
         <v>38</v>
       </c>
       <c r="B76" s="20"/>
       <c r="C76" s="20"/>
       <c r="D76" s="12"/>
-      <c r="E76" s="89"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="78" t="s">
+      <c r="E76" s="88"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="77" t="s">
         <v>38</v>
       </c>
-      <c r="B77" s="78"/>
-      <c r="C77" s="78"/>
-      <c r="D77" s="17">
-        <f>55821.88+14500</f>
-        <v>70321.88</v>
-      </c>
-      <c r="E77" s="98"/>
-    </row>
-    <row r="78" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="77"/>
-      <c r="B78" s="78"/>
-      <c r="C78" s="78"/>
+      <c r="B77" s="77"/>
+      <c r="C77" s="77"/>
+      <c r="D77" s="145">
+        <f>92201.5+29000</f>
+        <v>121201.5</v>
+      </c>
+      <c r="E77" s="97"/>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="76"/>
+      <c r="B78" s="77"/>
+      <c r="C78" s="77"/>
       <c r="D78" s="17"/>
-      <c r="E78" s="99"/>
-    </row>
-    <row r="79" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E78" s="98"/>
+    </row>
+    <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B79" s="20"/>
       <c r="C79" s="20"/>
       <c r="D79" s="12"/>
-      <c r="E79" s="89">
+      <c r="E79" s="88">
         <f>SUM(D77:D78)</f>
-        <v>70321.88</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="78"/>
-      <c r="B80" s="78"/>
-      <c r="C80" s="78"/>
-      <c r="D80" s="78"/>
-      <c r="E80" s="100"/>
-    </row>
-    <row r="81" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="101" t="s">
-        <v>194</v>
-      </c>
-      <c r="B81" s="101"/>
-      <c r="C81" s="101"/>
-      <c r="D81" s="102"/>
-      <c r="E81" s="103">
-        <v>4000000</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="104"/>
-      <c r="B82" s="71"/>
-      <c r="C82" s="71"/>
-      <c r="D82" s="71"/>
-      <c r="E82" s="105"/>
+        <v>121201.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="77"/>
+      <c r="B80" s="77"/>
+      <c r="C80" s="77"/>
+      <c r="D80" s="77"/>
+      <c r="E80" s="99"/>
+    </row>
+    <row r="81" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="100" t="s">
+        <v>183</v>
+      </c>
+      <c r="B81" s="100"/>
+      <c r="C81" s="100"/>
+      <c r="D81" s="101"/>
+      <c r="E81" s="102"/>
+    </row>
+    <row r="82" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="103"/>
+      <c r="B82" s="70"/>
+      <c r="C82" s="70"/>
+      <c r="D82" s="70"/>
+      <c r="E82" s="104"/>
       <c r="F82" s="31"/>
     </row>
-    <row r="83" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="106" t="s">
+    <row r="83" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="105" t="s">
         <v>39</v>
       </c>
-      <c r="B83" s="107"/>
-      <c r="C83" s="108"/>
-      <c r="D83" s="108"/>
-      <c r="E83" s="109">
+      <c r="B83" s="106"/>
+      <c r="C83" s="107"/>
+      <c r="D83" s="107"/>
+      <c r="E83" s="108">
         <f>(SUM(E30:E81))</f>
-        <v>7982024.3300000001</v>
+        <v>13140046.699999999</v>
       </c>
       <c r="F83" s="31"/>
       <c r="G83" s="31"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" s="71"/>
-      <c r="B84" s="71"/>
-      <c r="C84" s="71"/>
-      <c r="D84" s="71"/>
-      <c r="E84" s="71"/>
-    </row>
-    <row r="85" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="71"/>
-      <c r="B85" s="71"/>
-      <c r="C85" s="71"/>
-      <c r="D85" s="71"/>
-      <c r="E85" s="71"/>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="70"/>
+      <c r="B84" s="70"/>
+      <c r="C84" s="70"/>
+      <c r="D84" s="70"/>
+      <c r="E84" s="70"/>
+    </row>
+    <row r="85" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="70"/>
+      <c r="B85" s="70"/>
+      <c r="C85" s="70"/>
+      <c r="D85" s="70"/>
+      <c r="E85" s="70"/>
       <c r="F85" s="31"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" s="161" t="s">
-        <v>158</v>
-      </c>
-      <c r="B86" s="162"/>
-      <c r="C86" s="110"/>
-      <c r="D86" s="71"/>
-      <c r="E86" s="71"/>
-    </row>
-    <row r="87" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="153"/>
-      <c r="B87" s="154"/>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="158" t="s">
+        <v>154</v>
+      </c>
+      <c r="B86" s="159"/>
+      <c r="C86" s="109"/>
+      <c r="D86" s="70"/>
+      <c r="E86" s="70"/>
+    </row>
+    <row r="87" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="150"/>
+      <c r="B87" s="151"/>
       <c r="C87" s="17"/>
-      <c r="D87" s="71"/>
-      <c r="E87" s="71"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" s="155"/>
-      <c r="B88" s="156"/>
+      <c r="D87" s="70"/>
+      <c r="E87" s="70"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="152"/>
+      <c r="B88" s="153"/>
       <c r="C88" s="17"/>
-      <c r="D88" s="71"/>
-      <c r="E88" s="71"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="157"/>
-      <c r="B89" s="158"/>
-      <c r="C89" s="111"/>
-      <c r="D89" s="71"/>
-      <c r="E89" s="112"/>
-    </row>
-    <row r="90" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="159" t="s">
+      <c r="D88" s="70"/>
+      <c r="E88" s="70"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="154"/>
+      <c r="B89" s="155"/>
+      <c r="C89" s="110"/>
+      <c r="D89" s="70"/>
+      <c r="E89" s="111"/>
+    </row>
+    <row r="90" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="156" t="s">
         <v>16</v>
       </c>
-      <c r="B90" s="160"/>
-      <c r="C90" s="113">
+      <c r="B90" s="157"/>
+      <c r="C90" s="112">
         <f>SUM(C87:C89)</f>
         <v>0</v>
       </c>
-      <c r="D90" s="71"/>
-      <c r="E90" s="71"/>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="71"/>
-      <c r="B91" s="71"/>
-      <c r="C91" s="71"/>
-      <c r="D91" s="71"/>
-      <c r="E91" s="71"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92" s="114" t="s">
-        <v>163</v>
-      </c>
-      <c r="B92" s="114"/>
-      <c r="C92" s="115"/>
-      <c r="D92" s="116"/>
-      <c r="E92" s="71"/>
-    </row>
-    <row r="93" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="71"/>
-      <c r="B93" s="71"/>
-      <c r="C93" s="71"/>
-      <c r="D93" s="71"/>
-      <c r="E93" s="71"/>
-    </row>
-    <row r="94" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="117" t="s">
+      <c r="D90" s="70"/>
+      <c r="E90" s="70"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="70"/>
+      <c r="B91" s="70"/>
+      <c r="C91" s="70"/>
+      <c r="D91" s="70"/>
+      <c r="E91" s="70"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="113" t="s">
+        <v>159</v>
+      </c>
+      <c r="B92" s="113"/>
+      <c r="C92" s="114"/>
+      <c r="D92" s="115"/>
+      <c r="E92" s="70"/>
+    </row>
+    <row r="93" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="70"/>
+      <c r="B93" s="70"/>
+      <c r="C93" s="70"/>
+      <c r="D93" s="70"/>
+      <c r="E93" s="70"/>
+    </row>
+    <row r="94" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="116" t="s">
         <v>40</v>
       </c>
-      <c r="B94" s="118">
+      <c r="B94" s="117">
         <f>E83</f>
-        <v>7982024.3300000001</v>
-      </c>
-      <c r="C94" s="71"/>
-      <c r="D94" s="71"/>
-      <c r="E94" s="112"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95" s="119" t="s">
+        <v>13140046.699999999</v>
+      </c>
+      <c r="C94" s="70"/>
+      <c r="D94" s="70"/>
+      <c r="E94" s="111"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="B95" s="120">
+      <c r="B95" s="119">
         <f>E83-E81</f>
-        <v>3982024.33</v>
-      </c>
-      <c r="C95" s="71"/>
-      <c r="D95" s="71"/>
-      <c r="E95" s="71"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" s="121" t="s">
-        <v>160</v>
-      </c>
-      <c r="B96" s="122">
+        <v>13140046.699999999</v>
+      </c>
+      <c r="C95" s="70"/>
+      <c r="D95" s="70"/>
+      <c r="E95" s="70"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="120" t="s">
+        <v>156</v>
+      </c>
+      <c r="B96" s="121">
         <f>C90+C92</f>
         <v>0</v>
       </c>
-      <c r="C96" s="71"/>
-      <c r="D96" s="71"/>
-      <c r="E96" s="71"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="121" t="s">
-        <v>159</v>
-      </c>
-      <c r="B97" s="122">
+      <c r="C96" s="70"/>
+      <c r="D96" s="70"/>
+      <c r="E96" s="70"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="120" t="s">
+        <v>155</v>
+      </c>
+      <c r="B97" s="121">
         <f>C90</f>
         <v>0</v>
       </c>
-      <c r="C97" s="71"/>
-      <c r="D97" s="71"/>
-      <c r="E97" s="71"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="121" t="s">
-        <v>161</v>
-      </c>
-      <c r="B98" s="122">
+      <c r="C97" s="70"/>
+      <c r="D97" s="70"/>
+      <c r="E97" s="70"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="120" t="s">
+        <v>157</v>
+      </c>
+      <c r="B98" s="121">
         <f>B95+B97</f>
-        <v>3982024.33</v>
-      </c>
-      <c r="C98" s="71"/>
-      <c r="D98" s="71"/>
-      <c r="E98" s="71"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="71"/>
-      <c r="B99" s="71"/>
-      <c r="C99" s="71"/>
-      <c r="D99" s="71"/>
-      <c r="E99" s="71"/>
-    </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="152"/>
-      <c r="B100" s="152"/>
-      <c r="C100" s="152"/>
-      <c r="D100" s="71"/>
-      <c r="E100" s="71"/>
-    </row>
-    <row r="101" spans="1:5" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="152"/>
-      <c r="B101" s="152"/>
-      <c r="C101" s="152"/>
-      <c r="D101" s="71"/>
-      <c r="E101" s="71"/>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" s="71"/>
-      <c r="B102" s="71"/>
-      <c r="C102" s="71"/>
-      <c r="D102" s="71"/>
-      <c r="E102" s="71"/>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" s="123" t="s">
-        <v>176</v>
-      </c>
-      <c r="B103" s="124"/>
-      <c r="C103" s="125"/>
-      <c r="D103" s="71"/>
-      <c r="E103" s="71"/>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+        <v>13140046.699999999</v>
+      </c>
+      <c r="C98" s="70"/>
+      <c r="D98" s="70"/>
+      <c r="E98" s="70"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="70"/>
+      <c r="B99" s="70"/>
+      <c r="C99" s="70"/>
+      <c r="D99" s="70"/>
+      <c r="E99" s="70"/>
+    </row>
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="149"/>
+      <c r="B100" s="149"/>
+      <c r="C100" s="149"/>
+      <c r="D100" s="70"/>
+      <c r="E100" s="70"/>
+    </row>
+    <row r="101" spans="1:5" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="149"/>
+      <c r="B101" s="149"/>
+      <c r="C101" s="149"/>
+      <c r="D101" s="70"/>
+      <c r="E101" s="70"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="70"/>
+      <c r="B102" s="70"/>
+      <c r="C102" s="70"/>
+      <c r="D102" s="70"/>
+      <c r="E102" s="70"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="122" t="s">
+        <v>172</v>
+      </c>
+      <c r="B103" s="123"/>
+      <c r="C103" s="124"/>
+      <c r="D103" s="70"/>
+      <c r="E103" s="70"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B104" s="124">
-        <v>242274.94714675145</v>
-      </c>
-      <c r="C104" s="126"/>
-      <c r="D104" s="71"/>
-      <c r="E104" s="71"/>
-    </row>
-    <row r="105" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="127" t="s">
+      <c r="B104" s="123">
+        <v>535725.97893585078</v>
+      </c>
+      <c r="C104" s="125"/>
+      <c r="D104" s="70"/>
+      <c r="E104" s="70"/>
+    </row>
+    <row r="105" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="126" t="s">
         <v>44</v>
       </c>
-      <c r="B105" s="128">
+      <c r="B105" s="127">
         <f>PRORRATEO!I44</f>
-        <v>3413182.0317890993</v>
-      </c>
-      <c r="C105" s="125"/>
-      <c r="D105" s="112"/>
-      <c r="E105" s="71"/>
-    </row>
-    <row r="106" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="129" t="s">
+        <v>6668198.9696480017</v>
+      </c>
+      <c r="C105" s="124"/>
+      <c r="D105" s="111"/>
+      <c r="E105" s="70"/>
+    </row>
+    <row r="106" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="126" t="s">
+        <v>204</v>
+      </c>
+      <c r="B106" s="127">
+        <f>B113</f>
+        <v>614971.40413385991</v>
+      </c>
+      <c r="C106" s="124"/>
+      <c r="D106" s="111"/>
+      <c r="E106" s="70"/>
+    </row>
+    <row r="107" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="128" t="s">
         <v>43</v>
       </c>
-      <c r="B106" s="142">
-        <f>-(B98+B114)</f>
-        <v>-3632063.33</v>
-      </c>
-      <c r="C106" s="125"/>
-      <c r="D106" s="71"/>
-      <c r="E106" s="71"/>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" s="130" t="s">
+      <c r="B107" s="141">
+        <f>-(B98)</f>
+        <v>-13140046.699999999</v>
+      </c>
+      <c r="C107" s="124"/>
+      <c r="D107" s="70"/>
+      <c r="E107" s="70"/>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="129" t="s">
         <v>16</v>
       </c>
-      <c r="B107" s="42">
-        <f>SUM(B104:B106)</f>
-        <v>23393.64893585071</v>
-      </c>
-      <c r="C107" s="131"/>
-      <c r="D107" s="112"/>
-      <c r="E107" s="71"/>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="71"/>
-      <c r="B108" s="132"/>
-      <c r="C108" s="131"/>
-      <c r="D108" s="71"/>
-      <c r="E108" s="71"/>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="71"/>
-      <c r="B109" s="133"/>
-      <c r="C109" s="131"/>
-      <c r="D109" s="71"/>
-      <c r="E109" s="71"/>
-    </row>
-    <row r="110" spans="1:5" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="71"/>
+      <c r="B108" s="41">
+        <f>SUM(B104:B107)</f>
+        <v>-5321150.3472822867</v>
+      </c>
+      <c r="C108" s="130"/>
+      <c r="D108" s="111"/>
+      <c r="E108" s="70"/>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="70"/>
+      <c r="B109" s="131"/>
+      <c r="C109" s="130"/>
+      <c r="D109" s="70"/>
+      <c r="E109" s="70"/>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="70"/>
       <c r="B110" s="132"/>
-      <c r="C110" s="134"/>
-      <c r="D110" s="135"/>
-      <c r="E110" s="135"/>
-    </row>
-    <row r="111" spans="1:5" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="136" t="s">
+      <c r="C110" s="130"/>
+      <c r="D110" s="70"/>
+      <c r="E110" s="70"/>
+    </row>
+    <row r="111" spans="1:5" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="70"/>
+      <c r="B111" s="131"/>
+      <c r="C111" s="133"/>
+      <c r="D111" s="134"/>
+      <c r="E111" s="134"/>
+    </row>
+    <row r="112" spans="1:5" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="135" t="s">
         <v>45</v>
       </c>
-      <c r="B111" s="24"/>
-      <c r="C111" s="134"/>
-      <c r="D111" s="135"/>
-      <c r="E111" s="137"/>
-    </row>
-    <row r="112" spans="1:5" s="28" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="78" t="s">
+      <c r="B112" s="24"/>
+      <c r="C112" s="133"/>
+      <c r="D112" s="134"/>
+      <c r="E112" s="136"/>
+    </row>
+    <row r="113" spans="1:13" s="28" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="B112" s="24">
-        <v>436123.85052585986</v>
-      </c>
-      <c r="C112" s="134"/>
-      <c r="D112" s="137"/>
-      <c r="E112" s="137"/>
-    </row>
-    <row r="113" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="78" t="s">
+      <c r="B113" s="24">
+        <v>614971.40413385991</v>
+      </c>
+      <c r="C113" s="133"/>
+      <c r="D113" s="136"/>
+      <c r="E113" s="136"/>
+    </row>
+    <row r="114" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="B113" s="24">
+      <c r="B114" s="24">
         <f>PRORRATEO!I45</f>
-        <v>528808.55360800005</v>
-      </c>
-      <c r="C113" s="131"/>
-      <c r="D113" s="112"/>
-      <c r="E113" s="71"/>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A114" s="78" t="s">
-        <v>43</v>
-      </c>
-      <c r="B114" s="41">
-        <f>-(D44+D73+G38)</f>
-        <v>-349961</v>
-      </c>
-      <c r="C114" s="131"/>
-      <c r="D114" s="71"/>
-      <c r="E114" s="71"/>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A115" s="78"/>
-      <c r="B115" s="41"/>
-      <c r="C115" s="131"/>
-      <c r="D115" s="71"/>
-      <c r="E115" s="71"/>
-    </row>
-    <row r="116" spans="1:13" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="141"/>
-      <c r="B116" s="140"/>
-      <c r="C116" s="138"/>
-      <c r="D116" s="71"/>
-      <c r="E116" s="71"/>
-    </row>
-    <row r="117" spans="1:13" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="141"/>
-      <c r="B117" s="140"/>
-      <c r="C117" s="138"/>
-      <c r="D117" s="71"/>
-      <c r="E117" s="71"/>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A118" s="136" t="s">
+        <v>0</v>
+      </c>
+      <c r="C114" s="130"/>
+      <c r="D114" s="111"/>
+      <c r="E114" s="70"/>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" s="77" t="s">
+        <v>203</v>
+      </c>
+      <c r="B115" s="40">
+        <v>-614971.4</v>
+      </c>
+      <c r="C115" s="130"/>
+      <c r="D115" s="70"/>
+      <c r="E115" s="70"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="77"/>
+      <c r="B116" s="40"/>
+      <c r="C116" s="130"/>
+      <c r="D116" s="70"/>
+      <c r="E116" s="70"/>
+    </row>
+    <row r="117" spans="1:13" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="140"/>
+      <c r="B117" s="139"/>
+      <c r="C117" s="137"/>
+      <c r="D117" s="70"/>
+      <c r="E117" s="70"/>
+    </row>
+    <row r="118" spans="1:13" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="140"/>
+      <c r="B118" s="139"/>
+      <c r="C118" s="137"/>
+      <c r="D118" s="70"/>
+      <c r="E118" s="70"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="135" t="s">
         <v>46</v>
       </c>
-      <c r="B118" s="42">
-        <f>SUM(B112:B117)</f>
-        <v>614971.40413385991</v>
-      </c>
-      <c r="C118" s="125"/>
-      <c r="D118" s="71"/>
-      <c r="E118" s="71"/>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="71"/>
-      <c r="B119" s="71"/>
-      <c r="C119" s="71"/>
-      <c r="D119" s="71"/>
-      <c r="E119" s="71"/>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A121" s="149" t="s">
-        <v>164</v>
-      </c>
-      <c r="B121" s="149"/>
-      <c r="C121" s="149"/>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A122" s="149"/>
-      <c r="B122" s="149"/>
-      <c r="C122" s="149"/>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A123" s="1"/>
-      <c r="B123" s="1"/>
-      <c r="C123" s="23"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A124" s="32" t="s">
+      <c r="B119" s="41">
+        <f>SUM(B113:B118)</f>
+        <v>4.1338598821312189E-3</v>
+      </c>
+      <c r="C119" s="124"/>
+      <c r="D119" s="70"/>
+      <c r="E119" s="70"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="70"/>
+      <c r="B120" s="70"/>
+      <c r="C120" s="70"/>
+      <c r="D120" s="70"/>
+      <c r="E120" s="70"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" s="146" t="s">
+        <v>160</v>
+      </c>
+      <c r="B122" s="146"/>
+      <c r="C122" s="146"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" s="146"/>
+      <c r="B123" s="146"/>
+      <c r="C123" s="146"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" s="1"/>
+      <c r="B124" s="1"/>
+      <c r="C124" s="23"/>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B124" s="32"/>
-      <c r="C124" s="33">
-        <f>SUM(C123:C123)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M125" s="4"/>
+      <c r="B125" s="32"/>
+      <c r="C125" s="33">
+        <f>SUM(C124:C124)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M126" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A121:C122"/>
+    <mergeCell ref="A122:C123"/>
     <mergeCell ref="A15:E18"/>
     <mergeCell ref="A22:E26"/>
     <mergeCell ref="A87:B87"/>
@@ -3314,27 +3319,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5546875" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" customWidth="1"/>
-    <col min="6" max="6" width="6.5546875" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" customWidth="1"/>
-    <col min="9" max="9" width="5.44140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" customWidth="1"/>
+    <col min="9" max="9" width="12" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="5" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="14.6640625" customWidth="1"/>
-    <col min="15" max="15" width="14.5546875" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3353,7 +3358,7 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3367,14 +3372,14 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="39">
+      <c r="N2" s="38">
         <v>2902347.4099999997</v>
       </c>
-      <c r="O2" s="39">
+      <c r="O2" s="38">
         <v>7469692</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -3390,14 +3395,14 @@
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
-      <c r="N3" s="165">
+      <c r="N3" s="169">
         <f>O2</f>
         <v>7469692</v>
       </c>
-      <c r="O3" s="165"/>
+      <c r="O3" s="169"/>
       <c r="P3" s="5"/>
     </row>
-    <row r="4" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -3413,72 +3418,72 @@
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
-      <c r="N4" s="164"/>
-      <c r="O4" s="164"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="166" t="s">
+      <c r="N4" s="168"/>
+      <c r="O4" s="168"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="173" t="s">
+      <c r="B5" s="162" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="175" t="s">
+      <c r="C5" s="164" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="175" t="s">
+      <c r="D5" s="164" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="175" t="s">
-        <v>132</v>
-      </c>
-      <c r="F5" s="166" t="s">
+      <c r="E5" s="164" t="s">
+        <v>129</v>
+      </c>
+      <c r="F5" s="160" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="166" t="s">
+      <c r="G5" s="160" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="166" t="s">
+      <c r="H5" s="160" t="s">
         <v>13</v>
       </c>
       <c r="I5" s="14"/>
-      <c r="J5" s="170" t="s">
-        <v>147</v>
-      </c>
-      <c r="K5" s="168" t="s">
+      <c r="J5" s="172" t="s">
+        <v>143</v>
+      </c>
+      <c r="K5" s="170" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="168" t="s">
+      <c r="L5" s="170" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="168" t="s">
+      <c r="M5" s="170" t="s">
         <v>15</v>
       </c>
-      <c r="N5" s="168" t="s">
+      <c r="N5" s="170" t="s">
         <v>31</v>
       </c>
-      <c r="O5" s="168" t="s">
+      <c r="O5" s="170" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="167"/>
-      <c r="B6" s="174"/>
-      <c r="C6" s="176"/>
-      <c r="D6" s="176"/>
-      <c r="E6" s="177"/>
-      <c r="F6" s="167"/>
-      <c r="G6" s="167"/>
-      <c r="H6" s="167"/>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="161"/>
+      <c r="B6" s="163"/>
+      <c r="C6" s="165"/>
+      <c r="D6" s="165"/>
+      <c r="E6" s="166"/>
+      <c r="F6" s="161"/>
+      <c r="G6" s="161"/>
+      <c r="H6" s="161"/>
       <c r="I6" s="15"/>
-      <c r="J6" s="171"/>
-      <c r="K6" s="169"/>
-      <c r="L6" s="172"/>
-      <c r="M6" s="172"/>
-      <c r="N6" s="172"/>
-      <c r="O6" s="169"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="J6" s="173"/>
+      <c r="K6" s="171"/>
+      <c r="L6" s="174"/>
+      <c r="M6" s="174"/>
+      <c r="N6" s="174"/>
+      <c r="O6" s="171"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -3494,20 +3499,20 @@
         <v>2.63</v>
       </c>
       <c r="G7" s="24">
-        <v>121040.87763392553</v>
+        <v>196453.27475792554</v>
       </c>
       <c r="H7" s="29">
-        <f>168983+27536-G39</f>
-        <v>121040.50247600001</v>
+        <f>318956-G39</f>
+        <v>196453.05120000002</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J7" s="7">
         <f>H7-G7</f>
-        <v>-0.37515792551857885</v>
-      </c>
-      <c r="K7" s="40">
+        <v>-0.22355792552116327</v>
+      </c>
+      <c r="K7" s="39">
         <f>N$4*F7%</f>
         <v>0</v>
       </c>
@@ -3518,14 +3523,14 @@
       <c r="M7" s="23"/>
       <c r="N7" s="23">
         <f>L7+K7-J7+M7</f>
-        <v>196453.27475792554</v>
+        <v>196453.12315792553</v>
       </c>
       <c r="O7" s="23">
         <f>N7*6% + N7</f>
-        <v>208240.47124340106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+        <v>208240.31054740105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -3537,26 +3542,25 @@
         <v>85</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F8" s="1">
         <v>3.33</v>
       </c>
       <c r="G8" s="24">
-        <v>371337.89496694924</v>
+        <v>466820.63856694929</v>
       </c>
       <c r="H8" s="29">
-        <f>153258</f>
-        <v>153258</v>
+        <v>248741</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J8" s="7">
         <f t="shared" ref="J8:J42" si="0">H8-G8</f>
-        <v>-218079.89496694924</v>
-      </c>
-      <c r="K8" s="40">
+        <v>-218079.63856694929</v>
+      </c>
+      <c r="K8" s="39">
         <f t="shared" ref="K8:K42" si="1">N$4*F8%</f>
         <v>0</v>
       </c>
@@ -3567,18 +3571,15 @@
       <c r="M8" s="23"/>
       <c r="N8" s="23">
         <f>L8+K8-J8+M8</f>
-        <v>466820.63856694929</v>
+        <v>466820.38216694933</v>
       </c>
       <c r="O8" s="23">
         <f t="shared" ref="O8:O42" si="3">N8*6% + N8</f>
-        <v>494829.87688096624</v>
-      </c>
-      <c r="Q8" s="31">
-        <f>G7+G39</f>
-        <v>196519.37515792553</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+        <v>494829.60509696632</v>
+      </c>
+      <c r="Q8" s="31"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -3594,20 +3595,19 @@
         <v>3.32</v>
       </c>
       <c r="G9" s="24">
-        <v>152797.63821279994</v>
+        <v>247993.77439999999</v>
       </c>
       <c r="H9" s="29">
-        <f>G9</f>
-        <v>152797.63821279994</v>
+        <v>248000</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J9" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="40">
+        <v>6.2256000000052154</v>
+      </c>
+      <c r="K9" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3618,14 +3618,14 @@
       <c r="M9" s="23"/>
       <c r="N9" s="23">
         <f t="shared" ref="N9:N42" si="4">L9+K9-J9+M9</f>
-        <v>247993.77439999999</v>
+        <v>247987.54879999999</v>
       </c>
       <c r="O9" s="23">
         <f t="shared" si="3"/>
-        <v>262873.40086399997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+        <v>262866.80172799999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -3634,27 +3634,27 @@
         <v>51</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E10" s="34"/>
       <c r="F10" s="1">
         <v>3.42</v>
       </c>
       <c r="G10" s="24">
-        <v>512162.19533540343</v>
+        <v>610125.66173540347</v>
       </c>
       <c r="H10" s="29">
-        <f>150000+7500</f>
-        <v>157500</v>
+        <f>254000+1500</f>
+        <v>255500</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J10" s="7">
         <f t="shared" si="0"/>
-        <v>-354662.19533540343</v>
-      </c>
-      <c r="K10" s="40">
+        <v>-354625.66173540347</v>
+      </c>
+      <c r="K10" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3665,14 +3665,14 @@
       <c r="M10" s="23"/>
       <c r="N10" s="23">
         <f t="shared" si="4"/>
-        <v>610125.66173540347</v>
+        <v>610089.1281354035</v>
       </c>
       <c r="O10" s="23">
         <f t="shared" si="3"/>
-        <v>646733.20143952768</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+        <v>646694.47582352767</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -3688,20 +3688,20 @@
         <v>3.34</v>
       </c>
       <c r="G11" s="24">
-        <v>153718.403494</v>
+        <v>249487.71279999998</v>
       </c>
       <c r="H11" s="29">
         <f>G11</f>
-        <v>153718.403494</v>
+        <v>249487.71279999998</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J11" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K11" s="40">
+      <c r="K11" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3719,7 +3719,7 @@
         <v>264456.97556799999</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -3728,27 +3728,27 @@
         <v>53</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E12" s="34"/>
       <c r="F12" s="1">
         <v>3.33</v>
       </c>
       <c r="G12" s="24">
-        <v>153258.16875300001</v>
+        <v>248740.74360000002</v>
       </c>
       <c r="H12" s="29">
         <f>G12</f>
-        <v>153258.16875300001</v>
+        <v>248740.74360000002</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J12" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K12" s="40">
+      <c r="K12" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3766,7 +3766,7 @@
         <v>263665.18821600004</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
@@ -3782,20 +3782,20 @@
         <v>3.32</v>
       </c>
       <c r="G13" s="24">
-        <v>152797.93401200001</v>
+        <v>247993.77439999999</v>
       </c>
       <c r="H13" s="29">
         <f>G13</f>
-        <v>152797.93401200001</v>
+        <v>247993.77439999999</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J13" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K13" s="40">
+      <c r="K13" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>262873.40086399997</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
@@ -3829,20 +3829,20 @@
         <v>3.33</v>
       </c>
       <c r="G14" s="24">
-        <v>153258.16875300001</v>
+        <v>248740.74360000002</v>
       </c>
       <c r="H14" s="29">
         <f>G14</f>
-        <v>153258.16875300001</v>
+        <v>248740.74360000002</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J14" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K14" s="40">
+      <c r="K14" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3860,7 +3860,7 @@
         <v>263665.18821600004</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -3872,25 +3872,25 @@
         <v>90</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F15" s="1">
         <v>3.24</v>
       </c>
       <c r="G15" s="24">
-        <v>225650.79213000485</v>
+        <v>339447.8129300049</v>
       </c>
       <c r="H15" s="29">
-        <v>128221</v>
+        <v>242000</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J15" s="7">
         <f t="shared" si="0"/>
-        <v>-97429.792130004847</v>
-      </c>
-      <c r="K15" s="40">
+        <v>-97447.812930004904</v>
+      </c>
+      <c r="K15" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3901,17 +3901,17 @@
       <c r="M15" s="23"/>
       <c r="N15" s="23">
         <f t="shared" si="4"/>
-        <v>339447.8129300049</v>
+        <v>339465.83373000496</v>
       </c>
       <c r="O15" s="23">
         <f t="shared" si="3"/>
-        <v>359814.68170580518</v>
+        <v>359833.78375380527</v>
       </c>
       <c r="R15" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -3923,23 +3923,23 @@
         <v>91</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F16" s="1">
         <v>3.33</v>
       </c>
       <c r="G16" s="24">
-        <v>416823.23965319991</v>
+        <v>665563.98325319996</v>
       </c>
       <c r="H16" s="29"/>
       <c r="I16" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J16" s="7">
         <f t="shared" si="0"/>
-        <v>-416823.23965319991</v>
-      </c>
-      <c r="K16" s="40">
+        <v>-665563.98325319996</v>
+      </c>
+      <c r="K16" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3950,14 +3950,14 @@
       <c r="M16" s="23"/>
       <c r="N16" s="23">
         <f>L16+K16-J16+M16</f>
-        <v>665563.98325319996</v>
+        <v>914304.7268532</v>
       </c>
       <c r="O16" s="23">
         <f t="shared" si="3"/>
-        <v>705497.82224839192</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+        <v>969163.01046439202</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
@@ -3973,19 +3973,19 @@
         <v>3.32</v>
       </c>
       <c r="G17" s="24">
-        <v>161965.81005272001</v>
+        <v>257162.35445272</v>
       </c>
       <c r="H17" s="29">
-        <v>152797.23000000001</v>
+        <v>257162.35</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J17" s="7">
         <f t="shared" si="0"/>
-        <v>-9168.5800527200045</v>
-      </c>
-      <c r="K17" s="40">
+        <v>-4.4527199934236705E-3</v>
+      </c>
+      <c r="K17" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3996,14 +3996,14 @@
       <c r="M17" s="23"/>
       <c r="N17" s="23">
         <f t="shared" si="4"/>
-        <v>257162.35445272</v>
+        <v>247993.77885271999</v>
       </c>
       <c r="O17" s="23">
         <f t="shared" si="3"/>
-        <v>272592.09571988322</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+        <v>262873.40558388317</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>23</v>
       </c>
@@ -4019,20 +4019,19 @@
         <v>3.33</v>
       </c>
       <c r="G18" s="24">
-        <v>365040.24357039999</v>
+        <v>247740.74717040002</v>
       </c>
       <c r="H18" s="29">
-        <f>50040.24+316000</f>
-        <v>366040.24</v>
+        <v>22605.19</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J18" s="7">
         <f t="shared" si="0"/>
-        <v>999.99642959999619</v>
-      </c>
-      <c r="K18" s="40">
+        <v>-225135.55717040002</v>
+      </c>
+      <c r="K18" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4043,14 +4042,14 @@
       <c r="M18" s="23"/>
       <c r="N18" s="23">
         <f t="shared" si="4"/>
-        <v>247740.74717040002</v>
+        <v>473876.30077040003</v>
       </c>
       <c r="O18" s="23">
         <f t="shared" si="3"/>
-        <v>262605.19200062403</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+        <v>502308.87881662406</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
@@ -4066,20 +4065,20 @@
         <v>3.24</v>
       </c>
       <c r="G19" s="24">
-        <v>149214.9096347724</v>
+        <v>242011.42795877243</v>
       </c>
       <c r="H19" s="29">
-        <f>224700-H32</f>
-        <v>149221.50247599999</v>
+        <f>365000-H32</f>
+        <v>242497.05120000002</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J19" s="7">
         <f t="shared" si="0"/>
-        <v>6.5928412275970913</v>
-      </c>
-      <c r="K19" s="40">
+        <v>485.62324122758582</v>
+      </c>
+      <c r="K19" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4090,14 +4089,14 @@
       <c r="M19" s="23"/>
       <c r="N19" s="23">
         <f t="shared" si="4"/>
-        <v>242011.42795877243</v>
+        <v>241532.39755877244</v>
       </c>
       <c r="O19" s="23">
         <f t="shared" si="3"/>
-        <v>256532.11363629877</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+        <v>256024.34141229879</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
@@ -4109,26 +4108,25 @@
         <v>95</v>
       </c>
       <c r="E20" s="34" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F20" s="1">
         <v>3.33</v>
       </c>
       <c r="G20" s="24">
-        <v>153058.03420309996</v>
+        <v>248740.74360000002</v>
       </c>
       <c r="H20" s="29">
-        <f>G20</f>
-        <v>153058.03420309996</v>
+        <v>249000</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J20" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="40">
+        <v>259.25639999998384</v>
+      </c>
+      <c r="K20" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4139,14 +4137,14 @@
       <c r="M20" s="23"/>
       <c r="N20" s="23">
         <f t="shared" si="4"/>
-        <v>248740.74360000002</v>
+        <v>248481.48720000003</v>
       </c>
       <c r="O20" s="23">
         <f t="shared" si="3"/>
-        <v>263665.18821600004</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+        <v>263390.37643200002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -4162,17 +4160,17 @@
         <v>3.32</v>
       </c>
       <c r="G21" s="24">
-        <v>476571.93858125596</v>
+        <v>724565.71298125596</v>
       </c>
       <c r="H21" s="29"/>
       <c r="I21" s="13" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="J21" s="7">
         <f>H21-G21</f>
-        <v>-476571.93858125596</v>
-      </c>
-      <c r="K21" s="40">
+        <v>-724565.71298125596</v>
+      </c>
+      <c r="K21" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4183,14 +4181,14 @@
       <c r="M21" s="23"/>
       <c r="N21" s="23">
         <f t="shared" si="4"/>
-        <v>724565.71298125596</v>
+        <v>972559.48738125595</v>
       </c>
       <c r="O21" s="23">
         <f t="shared" si="3"/>
-        <v>768039.65576013131</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1030913.0566241313</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -4206,17 +4204,17 @@
         <v>3.33</v>
       </c>
       <c r="G22" s="13">
-        <v>2017145.2249669489</v>
+        <v>2265885.968566949</v>
       </c>
       <c r="H22" s="29"/>
       <c r="I22" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="J22" s="43">
+        <v>148</v>
+      </c>
+      <c r="J22" s="42">
         <f t="shared" si="0"/>
-        <v>-2017145.2249669489</v>
-      </c>
-      <c r="K22" s="40">
+        <v>-2265885.968566949</v>
+      </c>
+      <c r="K22" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4227,15 +4225,15 @@
       <c r="M22" s="23"/>
       <c r="N22" s="23">
         <f t="shared" si="4"/>
-        <v>2265885.968566949</v>
+        <v>2514626.7121669492</v>
       </c>
       <c r="O22" s="23">
         <f t="shared" si="3"/>
-        <v>2401839.126680966</v>
+        <v>2665504.3148969663</v>
       </c>
       <c r="R22" s="30"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>25</v>
       </c>
@@ -4247,26 +4245,26 @@
         <v>98</v>
       </c>
       <c r="E23" s="34" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F23" s="1">
         <v>3.24</v>
       </c>
       <c r="G23" s="24">
-        <v>149116.05608400004</v>
+        <v>256539.10204800003</v>
       </c>
       <c r="H23" s="29">
         <f>G23</f>
-        <v>149116.05608400004</v>
+        <v>256539.10204800003</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="J23" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K23" s="40">
+      <c r="K23" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4284,7 +4282,7 @@
         <v>256539.10204800003</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>26</v>
       </c>
@@ -4300,20 +4298,19 @@
         <v>3.24</v>
       </c>
       <c r="G24" s="24">
-        <v>141133.82077120009</v>
+        <v>256539.1</v>
       </c>
       <c r="H24" s="29">
-        <f>G24</f>
-        <v>141133.82077120009</v>
+        <v>257000</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="J24" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="40">
+        <v>460.89999999999418</v>
+      </c>
+      <c r="K24" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4324,14 +4321,14 @@
       <c r="M24" s="23"/>
       <c r="N24" s="23">
         <f t="shared" si="4"/>
-        <v>242018.02080000003</v>
+        <v>241557.12080000003</v>
       </c>
       <c r="O24" s="23">
         <f t="shared" si="3"/>
-        <v>256539.10204800003</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+        <v>256050.54804800003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -4343,26 +4340,26 @@
         <v>100</v>
       </c>
       <c r="E25" s="34" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F25" s="1">
         <v>3.32</v>
       </c>
       <c r="G25" s="24">
-        <v>152798.53402399988</v>
+        <v>247992.80594799988</v>
       </c>
       <c r="H25" s="29">
-        <f>228278-H33</f>
-        <v>152799.50247599999</v>
+        <f>370500-H33</f>
+        <v>247997.05120000002</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="J25" s="7">
         <f t="shared" si="0"/>
-        <v>0.96845200011739507</v>
-      </c>
-      <c r="K25" s="40">
+        <v>4.2452520001388621</v>
+      </c>
+      <c r="K25" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4373,14 +4370,14 @@
       <c r="M25" s="23"/>
       <c r="N25" s="23">
         <f t="shared" si="4"/>
-        <v>247992.80594799988</v>
+        <v>247989.52914799986</v>
       </c>
       <c r="O25" s="23">
         <f t="shared" si="3"/>
-        <v>262872.37430487986</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+        <v>262868.90089687984</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -4392,26 +4389,25 @@
         <v>101</v>
       </c>
       <c r="E26" s="34" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F26" s="1">
         <v>3.33</v>
       </c>
       <c r="G26" s="17">
-        <v>153258.16875300001</v>
+        <v>248740.74360000002</v>
       </c>
       <c r="H26" s="29">
-        <f>G26</f>
-        <v>153258.16875300001</v>
+        <v>248740</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="J26" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="40">
+        <v>-0.74360000001615845</v>
+      </c>
+      <c r="K26" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4422,14 +4418,14 @@
       <c r="M26" s="23"/>
       <c r="N26" s="23">
         <f t="shared" si="4"/>
-        <v>248740.74360000002</v>
+        <v>248741.48720000003</v>
       </c>
       <c r="O26" s="23">
         <f t="shared" si="3"/>
-        <v>263665.18821600004</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+        <v>263665.97643200005</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
@@ -4441,26 +4437,26 @@
         <v>102</v>
       </c>
       <c r="E27" s="34" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F27" s="1">
         <v>3.24</v>
       </c>
       <c r="G27" s="24">
-        <v>149116.05608400004</v>
+        <v>242018.02080000003</v>
       </c>
       <c r="H27" s="29">
         <f>G27</f>
-        <v>149116.05608400004</v>
+        <v>242018.02080000003</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="J27" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K27" s="40">
+      <c r="K27" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4478,7 +4474,7 @@
         <v>256539.10204800003</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
@@ -4494,20 +4490,20 @@
         <v>3.33</v>
       </c>
       <c r="G28" s="24">
-        <v>153258.16875300001</v>
+        <v>248741.90740100003</v>
       </c>
       <c r="H28" s="29">
-        <f>304214-H37-H36</f>
-        <v>153257.00495199999</v>
+        <f>493747-H37-H36</f>
+        <v>248741.1024</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="J28" s="7">
         <f t="shared" si="0"/>
-        <v>-1.1638010000169743</v>
-      </c>
-      <c r="K28" s="40">
+        <v>-0.8050010000297334</v>
+      </c>
+      <c r="K28" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4518,14 +4514,14 @@
       <c r="M28" s="23"/>
       <c r="N28" s="23">
         <f t="shared" si="4"/>
-        <v>248741.90740100003</v>
+        <v>248741.54860100005</v>
       </c>
       <c r="O28" s="23">
         <f t="shared" si="3"/>
-        <v>263666.42184506002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+        <v>263666.04151706008</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
@@ -4537,23 +4533,26 @@
         <v>104</v>
       </c>
       <c r="E29" s="34" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="F29" s="1">
         <v>3.32</v>
       </c>
-      <c r="G29" s="146">
-        <v>284184.72611239995</v>
-      </c>
-      <c r="H29" s="147"/>
+      <c r="G29" s="17">
+        <v>532178.50051239994</v>
+      </c>
+      <c r="H29" s="29">
+        <f>400791.71+131386.79</f>
+        <v>532178.5</v>
+      </c>
       <c r="I29" s="13" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="J29" s="7">
         <f t="shared" si="0"/>
-        <v>-284184.72611239995</v>
-      </c>
-      <c r="K29" s="40">
+        <v>-5.123999435454607E-4</v>
+      </c>
+      <c r="K29" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4564,17 +4563,17 @@
       <c r="M29" s="23"/>
       <c r="N29" s="23">
         <f t="shared" si="4"/>
-        <v>532178.50051239994</v>
+        <v>247993.77491239994</v>
       </c>
       <c r="O29" s="23">
         <f t="shared" si="3"/>
-        <v>564109.21054314391</v>
-      </c>
-      <c r="Q29" s="148" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+        <v>262873.40140714392</v>
+      </c>
+      <c r="Q29" s="144" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>36</v>
       </c>
@@ -4586,26 +4585,26 @@
         <v>105</v>
       </c>
       <c r="E30" s="34" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F30" s="1">
         <v>3.33</v>
       </c>
       <c r="G30" s="24">
-        <v>153258.16875300001</v>
+        <v>248740.74360000002</v>
       </c>
       <c r="H30" s="29">
         <f>G30</f>
-        <v>153258.16875300001</v>
+        <v>248740.74360000002</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="J30" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K30" s="40">
+      <c r="K30" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4622,11 +4621,11 @@
         <f t="shared" si="3"/>
         <v>263665.18821600004</v>
       </c>
-      <c r="Q30" s="148" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q30" s="144" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>36</v>
       </c>
@@ -4634,27 +4633,29 @@
       <c r="C31" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="D31" s="144" t="s">
-        <v>186</v>
-      </c>
-      <c r="E31" s="35"/>
+      <c r="D31" s="143" t="s">
+        <v>202</v>
+      </c>
+      <c r="E31" s="34" t="s">
+        <v>201</v>
+      </c>
       <c r="F31" s="1">
         <v>3.24</v>
       </c>
       <c r="G31" s="24">
-        <v>783395.0121480932</v>
+        <v>876297.03294809326</v>
       </c>
       <c r="H31" s="29">
-        <v>149116</v>
+        <v>242018</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="J31" s="7">
         <f t="shared" si="0"/>
-        <v>-634279.0121480932</v>
-      </c>
-      <c r="K31" s="40">
+        <v>-634279.03294809326</v>
+      </c>
+      <c r="K31" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4665,14 +4666,14 @@
       <c r="M31" s="23"/>
       <c r="N31" s="23">
         <f>L31+K31-J31+M31</f>
-        <v>876297.03294809326</v>
+        <v>876297.05374809331</v>
       </c>
       <c r="O31" s="23">
         <f t="shared" si="3"/>
-        <v>928874.8549249788</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+        <v>928874.87697297893</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>36</v>
       </c>
@@ -4688,20 +4689,20 @@
         <v>1.64</v>
       </c>
       <c r="G32" s="24">
-        <v>75478.497523999991</v>
+        <v>122502.94879999998</v>
       </c>
       <c r="H32" s="29">
         <f>G32</f>
-        <v>75478.497523999991</v>
+        <v>122502.94879999998</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="J32" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K32" s="40">
+      <c r="K32" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4719,7 +4720,7 @@
         <v>129853.12572799998</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
@@ -4735,20 +4736,20 @@
         <v>1.64</v>
       </c>
       <c r="G33" s="24">
-        <v>75478.497523999991</v>
+        <v>122502.94879999998</v>
       </c>
       <c r="H33" s="29">
         <f>G33</f>
-        <v>75478.497523999991</v>
+        <v>122502.94879999998</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="J33" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K33" s="40">
+      <c r="K33" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4766,7 +4767,7 @@
         <v>129853.12572799998</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>36</v>
       </c>
@@ -4782,19 +4783,19 @@
         <v>1.64</v>
       </c>
       <c r="G34" s="24">
-        <v>74663.836837367257</v>
+        <v>132166.78563736723</v>
       </c>
       <c r="H34" s="29">
         <v>65000</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="J34" s="7">
         <f t="shared" si="0"/>
-        <v>-9663.8368373672565</v>
-      </c>
-      <c r="K34" s="40">
+        <v>-67166.785637367226</v>
+      </c>
+      <c r="K34" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4805,14 +4806,14 @@
       <c r="M34" s="23"/>
       <c r="N34" s="23">
         <f t="shared" si="4"/>
-        <v>132166.78563736723</v>
+        <v>189669.73443736721</v>
       </c>
       <c r="O34" s="23">
         <f t="shared" si="3"/>
-        <v>140096.79277560927</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+        <v>201049.91850360925</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
@@ -4828,17 +4829,17 @@
         <v>1.64</v>
       </c>
       <c r="G35" s="24">
-        <v>140380.40687479998</v>
+        <v>262883.3556748</v>
       </c>
       <c r="H35" s="29"/>
       <c r="I35" s="13" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="J35" s="7">
         <f t="shared" si="0"/>
-        <v>-140380.40687479998</v>
-      </c>
-      <c r="K35" s="40">
+        <v>-262883.3556748</v>
+      </c>
+      <c r="K35" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4849,17 +4850,17 @@
       <c r="M35" s="23"/>
       <c r="N35" s="23">
         <f t="shared" si="4"/>
-        <v>262883.3556748</v>
+        <v>385386.30447480001</v>
       </c>
       <c r="O35" s="23">
         <f t="shared" si="3"/>
-        <v>278656.35701528797</v>
+        <v>408509.48274328798</v>
       </c>
       <c r="Q35" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>36</v>
       </c>
@@ -4875,20 +4876,20 @@
         <v>1.64</v>
       </c>
       <c r="G36" s="24">
-        <v>75478.497523999991</v>
+        <v>122502.94879999998</v>
       </c>
       <c r="H36" s="29">
         <f>G36</f>
-        <v>75478.497523999991</v>
+        <v>122502.94879999998</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="J36" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K36" s="40">
+      <c r="K36" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4906,7 +4907,7 @@
         <v>129853.12572799998</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
@@ -4922,20 +4923,20 @@
         <v>1.64</v>
       </c>
       <c r="G37" s="24">
-        <v>75478.497523999991</v>
+        <v>122502.94879999998</v>
       </c>
       <c r="H37" s="29">
         <f>G37</f>
-        <v>75478.497523999991</v>
+        <v>122502.94879999998</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="J37" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K37" s="40">
+      <c r="K37" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4953,7 +4954,7 @@
         <v>129853.12572799998</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
@@ -4968,18 +4969,18 @@
       <c r="F38" s="1">
         <v>1.64</v>
       </c>
-      <c r="G38" s="24">
-        <v>993428.88502876763</v>
+      <c r="G38" s="190">
+        <v>1115931.8338287675</v>
       </c>
       <c r="H38" s="29"/>
       <c r="I38" s="13" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="J38" s="7">
         <f t="shared" si="0"/>
-        <v>-993428.88502876763</v>
-      </c>
-      <c r="K38" s="40">
+        <v>-1115931.8338287675</v>
+      </c>
+      <c r="K38" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4990,14 +4991,14 @@
       <c r="M38" s="23"/>
       <c r="N38" s="23">
         <f t="shared" si="4"/>
-        <v>1115931.8338287675</v>
+        <v>1238434.7826287674</v>
       </c>
       <c r="O38" s="23">
         <f t="shared" si="3"/>
-        <v>1182887.7438584936</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+        <v>1312740.8695864934</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>36</v>
       </c>
@@ -5013,20 +5014,20 @@
         <v>1.64</v>
       </c>
       <c r="G39" s="24">
-        <v>75478.497523999991</v>
+        <v>122502.94879999998</v>
       </c>
       <c r="H39" s="29">
         <f>G39</f>
-        <v>75478.497523999991</v>
+        <v>122502.94879999998</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="J39" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K39" s="40">
+      <c r="K39" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5044,7 +5045,7 @@
         <v>129853.12572799998</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>36</v>
       </c>
@@ -5056,26 +5057,26 @@
         <v>106</v>
       </c>
       <c r="E40" s="34" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F40" s="1">
         <v>1.64</v>
       </c>
       <c r="G40" s="24">
-        <v>75478.497523999991</v>
+        <v>122502.94879999998</v>
       </c>
       <c r="H40" s="29">
         <f>G40</f>
-        <v>75478.497523999991</v>
+        <v>122502.94879999998</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="J40" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K40" s="40">
+      <c r="K40" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5093,7 +5094,7 @@
         <v>129853.12572799998</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>36</v>
       </c>
@@ -5109,19 +5110,20 @@
         <v>1.64</v>
       </c>
       <c r="G41" s="24">
-        <v>71790.46400559989</v>
+        <v>118195.41280559987</v>
       </c>
       <c r="H41" s="29">
-        <v>76098</v>
+        <f>45287.14+80000</f>
+        <v>125287.14</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="J41" s="7">
-        <f t="shared" si="0"/>
-        <v>4307.5359944001102</v>
-      </c>
-      <c r="K41" s="40">
+        <f>H41-G41</f>
+        <v>7091.7271944001259</v>
+      </c>
+      <c r="K41" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5132,14 +5134,14 @@
       <c r="M41" s="23"/>
       <c r="N41" s="23">
         <f t="shared" si="4"/>
-        <v>118195.41280559987</v>
+        <v>115411.22160559986</v>
       </c>
       <c r="O41" s="23">
         <f t="shared" si="3"/>
-        <v>125287.13757393586</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+        <v>122335.89490193586</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>36</v>
       </c>
@@ -5155,17 +5157,19 @@
         <v>1.64</v>
       </c>
       <c r="G42" s="24">
-        <v>138798.22557639994</v>
-      </c>
-      <c r="H42" s="29"/>
+        <v>276979.24483898393</v>
+      </c>
+      <c r="H42" s="29">
+        <v>262000</v>
+      </c>
       <c r="I42" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J42" s="7">
         <f t="shared" si="0"/>
-        <v>-138798.22557639994</v>
-      </c>
-      <c r="K42" s="40">
+        <v>-14979.244838983926</v>
+      </c>
+      <c r="K42" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5176,14 +5180,14 @@
       <c r="M42" s="23"/>
       <c r="N42" s="23">
         <f t="shared" si="4"/>
-        <v>261301.17437639993</v>
+        <v>137482.19363898391</v>
       </c>
       <c r="O42" s="23">
         <f t="shared" si="3"/>
-        <v>276979.24483898393</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>145731.12525732294</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -5195,16 +5199,16 @@
       </c>
       <c r="G43" s="9">
         <f>SUM(G7:G42)</f>
-        <v>9727292.9889031108</v>
+        <v>13306437.357216589</v>
       </c>
       <c r="H43" s="9">
         <f>SUM(H7:H42)</f>
-        <v>3941990.5853970982</v>
+        <v>6668198.9696480017</v>
       </c>
       <c r="I43" s="9"/>
-      <c r="J43" s="139">
+      <c r="J43" s="138">
         <f t="shared" ref="J43:O43" si="5">SUM(J7:J42)</f>
-        <v>-5785302.403506008</v>
+        <v>-6638238.3875685921</v>
       </c>
       <c r="K43" s="9">
         <f t="shared" si="5"/>
@@ -5220,129 +5224,123 @@
       </c>
       <c r="N43" s="10">
         <f t="shared" si="5"/>
-        <v>13261717.126306005</v>
+        <v>14114653.110368587</v>
       </c>
       <c r="O43" s="9">
         <f t="shared" si="5"/>
-        <v>14057420.15388437</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>14961532.296990706</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="G44" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I44">
         <f>SUMIF(I7:I42,"b",H7:H42)</f>
-        <v>3413182.0317890993</v>
+        <v>6668198.9696480017</v>
       </c>
       <c r="L44" s="11"/>
     </row>
-    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="G45" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I45">
         <f>SUMIF(I7:I42,"e",H7:H42)</f>
-        <v>528808.55360800005</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="G46" t="s">
         <v>16</v>
       </c>
-      <c r="H46" s="36">
+      <c r="H46" s="35">
         <f>I44+I45</f>
-        <v>3941990.5853970991</v>
-      </c>
-    </row>
-    <row r="49" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D49" s="163" t="s">
-        <v>182</v>
-      </c>
-      <c r="E49" s="163"/>
-      <c r="F49" s="163"/>
-      <c r="G49" s="163"/>
-      <c r="H49" s="163"/>
-      <c r="I49" s="163"/>
-      <c r="J49" s="163"/>
-      <c r="K49" s="163"/>
-      <c r="L49" s="163"/>
-      <c r="M49" s="163"/>
-      <c r="N49" s="163"/>
-    </row>
-    <row r="50" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D50" s="163"/>
-      <c r="E50" s="163"/>
-      <c r="F50" s="163"/>
-      <c r="G50" s="163"/>
-      <c r="H50" s="163"/>
-      <c r="I50" s="163"/>
-      <c r="J50" s="163"/>
-      <c r="K50" s="163"/>
-      <c r="L50" s="163"/>
-      <c r="M50" s="163"/>
-      <c r="N50" s="163"/>
-    </row>
-    <row r="51" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D51" s="163"/>
-      <c r="E51" s="163"/>
-      <c r="F51" s="163"/>
-      <c r="G51" s="163"/>
-      <c r="H51" s="163"/>
-      <c r="I51" s="163"/>
-      <c r="J51" s="163"/>
-      <c r="K51" s="163"/>
-      <c r="L51" s="163"/>
-      <c r="M51" s="163"/>
-      <c r="N51" s="163"/>
-    </row>
-    <row r="52" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D52" s="163"/>
-      <c r="E52" s="163"/>
-      <c r="F52" s="163"/>
-      <c r="G52" s="163"/>
-      <c r="H52" s="163"/>
-      <c r="I52" s="163"/>
-      <c r="J52" s="163"/>
-      <c r="K52" s="163"/>
-      <c r="L52" s="163"/>
-      <c r="M52" s="163"/>
-      <c r="N52" s="163"/>
-    </row>
-    <row r="53" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D53" s="163"/>
-      <c r="E53" s="163"/>
-      <c r="F53" s="163"/>
-      <c r="G53" s="163"/>
-      <c r="H53" s="163"/>
-      <c r="I53" s="163"/>
-      <c r="J53" s="163"/>
-      <c r="K53" s="163"/>
-      <c r="L53" s="163"/>
-      <c r="M53" s="163"/>
-      <c r="N53" s="163"/>
-    </row>
-    <row r="54" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D54" s="163"/>
-      <c r="E54" s="163"/>
-      <c r="F54" s="163"/>
-      <c r="G54" s="163"/>
-      <c r="H54" s="163"/>
-      <c r="I54" s="163"/>
-      <c r="J54" s="163"/>
-      <c r="K54" s="163"/>
-      <c r="L54" s="163"/>
-      <c r="M54" s="163"/>
-      <c r="N54" s="163"/>
+        <v>6668198.9696480017</v>
+      </c>
+    </row>
+    <row r="49" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D49" s="167" t="s">
+        <v>178</v>
+      </c>
+      <c r="E49" s="167"/>
+      <c r="F49" s="167"/>
+      <c r="G49" s="167"/>
+      <c r="H49" s="167"/>
+      <c r="I49" s="167"/>
+      <c r="J49" s="167"/>
+      <c r="K49" s="167"/>
+      <c r="L49" s="167"/>
+      <c r="M49" s="167"/>
+      <c r="N49" s="167"/>
+    </row>
+    <row r="50" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D50" s="167"/>
+      <c r="E50" s="167"/>
+      <c r="F50" s="167"/>
+      <c r="G50" s="167"/>
+      <c r="H50" s="167"/>
+      <c r="I50" s="167"/>
+      <c r="J50" s="167"/>
+      <c r="K50" s="167"/>
+      <c r="L50" s="167"/>
+      <c r="M50" s="167"/>
+      <c r="N50" s="167"/>
+    </row>
+    <row r="51" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D51" s="167"/>
+      <c r="E51" s="167"/>
+      <c r="F51" s="167"/>
+      <c r="G51" s="167"/>
+      <c r="H51" s="167"/>
+      <c r="I51" s="167"/>
+      <c r="J51" s="167"/>
+      <c r="K51" s="167"/>
+      <c r="L51" s="167"/>
+      <c r="M51" s="167"/>
+      <c r="N51" s="167"/>
+    </row>
+    <row r="52" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D52" s="167"/>
+      <c r="E52" s="167"/>
+      <c r="F52" s="167"/>
+      <c r="G52" s="167"/>
+      <c r="H52" s="167"/>
+      <c r="I52" s="167"/>
+      <c r="J52" s="167"/>
+      <c r="K52" s="167"/>
+      <c r="L52" s="167"/>
+      <c r="M52" s="167"/>
+      <c r="N52" s="167"/>
+    </row>
+    <row r="53" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D53" s="167"/>
+      <c r="E53" s="167"/>
+      <c r="F53" s="167"/>
+      <c r="G53" s="167"/>
+      <c r="H53" s="167"/>
+      <c r="I53" s="167"/>
+      <c r="J53" s="167"/>
+      <c r="K53" s="167"/>
+      <c r="L53" s="167"/>
+      <c r="M53" s="167"/>
+      <c r="N53" s="167"/>
+    </row>
+    <row r="54" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D54" s="167"/>
+      <c r="E54" s="167"/>
+      <c r="F54" s="167"/>
+      <c r="G54" s="167"/>
+      <c r="H54" s="167"/>
+      <c r="I54" s="167"/>
+      <c r="J54" s="167"/>
+      <c r="K54" s="167"/>
+      <c r="L54" s="167"/>
+      <c r="M54" s="167"/>
+      <c r="N54" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="D49:N54"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="N3:O3"/>
@@ -5354,6 +5352,12 @@
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -5363,380 +5367,380 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="E6:O38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="6" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E7" s="185" t="s">
+    <row r="6" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E7" s="182" t="s">
+        <v>161</v>
+      </c>
+      <c r="F7" s="183"/>
+      <c r="G7" s="183"/>
+      <c r="H7" s="183"/>
+      <c r="I7" s="183"/>
+      <c r="J7" s="183"/>
+      <c r="K7" s="181"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="44"/>
+    </row>
+    <row r="8" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E8" s="184" t="s">
+        <v>162</v>
+      </c>
+      <c r="F8" s="183"/>
+      <c r="G8" s="183"/>
+      <c r="H8" s="183"/>
+      <c r="I8" s="183"/>
+      <c r="J8" s="183"/>
+      <c r="K8" s="181"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="46"/>
+    </row>
+    <row r="9" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E9" s="43"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="K9" s="46"/>
+      <c r="L9" s="45"/>
+      <c r="M9" s="46"/>
+    </row>
+    <row r="10" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E10" s="45" t="s">
+        <v>164</v>
+      </c>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="F7" s="186"/>
-      <c r="G7" s="186"/>
-      <c r="H7" s="186"/>
-      <c r="I7" s="186"/>
-      <c r="J7" s="186"/>
-      <c r="K7" s="184"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="45"/>
-    </row>
-    <row r="8" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E8" s="187" t="s">
+      <c r="K10" s="46"/>
+      <c r="L10" s="45"/>
+      <c r="M10" s="46"/>
+    </row>
+    <row r="11" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E11" s="49"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="50"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="45"/>
+      <c r="M11" s="46"/>
+    </row>
+    <row r="12" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E12" s="185" t="s">
         <v>166</v>
       </c>
-      <c r="F8" s="186"/>
-      <c r="G8" s="186"/>
-      <c r="H8" s="186"/>
-      <c r="I8" s="186"/>
-      <c r="J8" s="186"/>
-      <c r="K8" s="184"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="47"/>
-    </row>
-    <row r="9" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E9" s="44"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="49" t="s">
+      <c r="F12" s="186"/>
+      <c r="G12" s="186"/>
+      <c r="H12" s="186"/>
+      <c r="I12" s="186"/>
+      <c r="J12" s="186"/>
+      <c r="K12" s="187"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="46"/>
+    </row>
+    <row r="13" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E13" s="45"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="46"/>
+      <c r="L13" s="45"/>
+      <c r="M13" s="46"/>
+    </row>
+    <row r="14" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E14" s="45" t="s">
         <v>167</v>
       </c>
-      <c r="K9" s="47"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="47"/>
-    </row>
-    <row r="10" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E10" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49" t="s">
-        <v>169</v>
-      </c>
-      <c r="K10" s="47"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="47"/>
-    </row>
-    <row r="11" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E11" s="50"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="52"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="47"/>
-    </row>
-    <row r="12" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E12" s="188" t="s">
-        <v>170</v>
-      </c>
-      <c r="F12" s="189"/>
-      <c r="G12" s="189"/>
-      <c r="H12" s="189"/>
-      <c r="I12" s="189"/>
-      <c r="J12" s="189"/>
-      <c r="K12" s="190"/>
-      <c r="L12" s="46"/>
-      <c r="M12" s="47"/>
-    </row>
-    <row r="13" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E13" s="46"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="47"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="47"/>
-    </row>
-    <row r="14" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E14" s="46" t="s">
-        <v>171</v>
-      </c>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49" t="str">
+      <c r="F14" s="48"/>
+      <c r="G14" s="48" t="str">
         <f>PRORRATEO!D12</f>
         <v>RAMOS PAMELA</v>
       </c>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49" t="s">
-        <v>172</v>
-      </c>
-      <c r="J14" s="53">
+      <c r="H14" s="48"/>
+      <c r="I14" s="48" t="s">
+        <v>168</v>
+      </c>
+      <c r="J14" s="52">
         <v>45600</v>
       </c>
-      <c r="K14" s="47"/>
-      <c r="L14" s="178" t="s">
-        <v>173</v>
-      </c>
-      <c r="M14" s="179"/>
-    </row>
-    <row r="15" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E15" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="F15" s="54" t="str">
+      <c r="K14" s="46"/>
+      <c r="L14" s="175" t="s">
+        <v>169</v>
+      </c>
+      <c r="M14" s="176"/>
+    </row>
+    <row r="15" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E15" s="45" t="s">
+        <v>170</v>
+      </c>
+      <c r="F15" s="53" t="str">
         <f>PRORRATEO!C12</f>
         <v>2A</v>
       </c>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="47"/>
-    </row>
-    <row r="16" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E16" s="46"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="49"/>
-      <c r="J16" s="49"/>
-      <c r="K16" s="47"/>
-      <c r="L16" s="180"/>
-      <c r="M16" s="179"/>
-    </row>
-    <row r="17" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="E17" s="46"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="49"/>
-      <c r="K17" s="47"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="47"/>
-    </row>
-    <row r="18" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="E18" s="46"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="49"/>
-      <c r="K18" s="47"/>
-      <c r="L18" s="46"/>
-      <c r="M18" s="47"/>
-    </row>
-    <row r="19" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E19" s="46"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="47"/>
-      <c r="L19" s="55"/>
-      <c r="M19" s="56"/>
-    </row>
-    <row r="20" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E20" s="181" t="s">
-        <v>175</v>
-      </c>
-      <c r="F20" s="182"/>
-      <c r="G20" s="182"/>
-      <c r="H20" s="182"/>
-      <c r="I20" s="182"/>
-      <c r="J20" s="183">
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="46"/>
+      <c r="L15" s="45"/>
+      <c r="M15" s="46"/>
+    </row>
+    <row r="16" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E16" s="45"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="48"/>
+      <c r="K16" s="46"/>
+      <c r="L16" s="177"/>
+      <c r="M16" s="176"/>
+    </row>
+    <row r="17" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E17" s="45"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="46"/>
+      <c r="L17" s="45"/>
+      <c r="M17" s="46"/>
+    </row>
+    <row r="18" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E18" s="45"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="46"/>
+      <c r="L18" s="45"/>
+      <c r="M18" s="46"/>
+    </row>
+    <row r="19" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E19" s="45"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="54"/>
+      <c r="M19" s="55"/>
+    </row>
+    <row r="20" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E20" s="178" t="s">
+        <v>171</v>
+      </c>
+      <c r="F20" s="179"/>
+      <c r="G20" s="179"/>
+      <c r="H20" s="179"/>
+      <c r="I20" s="179"/>
+      <c r="J20" s="180">
         <f>PRORRATEO!H12</f>
-        <v>153258.16875300001</v>
-      </c>
-      <c r="K20" s="184"/>
-      <c r="L20" s="57"/>
-      <c r="M20" s="58"/>
-    </row>
-    <row r="24" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G25" s="185" t="s">
+        <v>248740.74360000002</v>
+      </c>
+      <c r="K20" s="181"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="57"/>
+    </row>
+    <row r="24" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G25" s="182" t="s">
+        <v>161</v>
+      </c>
+      <c r="H25" s="183"/>
+      <c r="I25" s="183"/>
+      <c r="J25" s="183"/>
+      <c r="K25" s="183"/>
+      <c r="L25" s="183"/>
+      <c r="M25" s="181"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="44"/>
+    </row>
+    <row r="26" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G26" s="184" t="s">
+        <v>162</v>
+      </c>
+      <c r="H26" s="183"/>
+      <c r="I26" s="183"/>
+      <c r="J26" s="183"/>
+      <c r="K26" s="183"/>
+      <c r="L26" s="183"/>
+      <c r="M26" s="181"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="46"/>
+    </row>
+    <row r="27" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="G27" s="43"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="47"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="M27" s="46"/>
+      <c r="N27" s="45"/>
+      <c r="O27" s="46"/>
+    </row>
+    <row r="28" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="G28" s="45" t="s">
+        <v>164</v>
+      </c>
+      <c r="H28" s="48"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="48"/>
+      <c r="K28" s="48"/>
+      <c r="L28" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="H25" s="186"/>
-      <c r="I25" s="186"/>
-      <c r="J25" s="186"/>
-      <c r="K25" s="186"/>
-      <c r="L25" s="186"/>
-      <c r="M25" s="184"/>
-      <c r="N25" s="44"/>
-      <c r="O25" s="45"/>
-    </row>
-    <row r="26" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G26" s="187" t="s">
+      <c r="M28" s="46"/>
+      <c r="N28" s="45"/>
+      <c r="O28" s="46"/>
+    </row>
+    <row r="29" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="G29" s="49"/>
+      <c r="H29" s="50"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="50"/>
+      <c r="K29" s="50"/>
+      <c r="L29" s="50"/>
+      <c r="M29" s="51"/>
+      <c r="N29" s="45"/>
+      <c r="O29" s="46"/>
+    </row>
+    <row r="30" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="G30" s="185" t="s">
         <v>166</v>
       </c>
-      <c r="H26" s="186"/>
-      <c r="I26" s="186"/>
-      <c r="J26" s="186"/>
-      <c r="K26" s="186"/>
-      <c r="L26" s="186"/>
-      <c r="M26" s="184"/>
-      <c r="N26" s="46"/>
-      <c r="O26" s="47"/>
-    </row>
-    <row r="27" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="G27" s="44"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="48"/>
-      <c r="K27" s="49"/>
-      <c r="L27" s="49" t="s">
+      <c r="H30" s="186"/>
+      <c r="I30" s="186"/>
+      <c r="J30" s="186"/>
+      <c r="K30" s="186"/>
+      <c r="L30" s="186"/>
+      <c r="M30" s="187"/>
+      <c r="N30" s="45"/>
+      <c r="O30" s="46"/>
+    </row>
+    <row r="31" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="G31" s="45"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="48"/>
+      <c r="J31" s="48"/>
+      <c r="K31" s="48"/>
+      <c r="L31" s="48"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="45"/>
+      <c r="O31" s="46"/>
+    </row>
+    <row r="32" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="G32" s="45" t="s">
         <v>167</v>
       </c>
-      <c r="M27" s="47"/>
-      <c r="N27" s="46"/>
-      <c r="O27" s="47"/>
-    </row>
-    <row r="28" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="G28" s="46" t="s">
+      <c r="H32" s="48"/>
+      <c r="I32" s="48"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="48" t="s">
         <v>168</v>
       </c>
-      <c r="H28" s="49"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="49"/>
-      <c r="K28" s="49"/>
-      <c r="L28" s="49" t="s">
+      <c r="L32" s="52">
+        <v>45600</v>
+      </c>
+      <c r="M32" s="46"/>
+      <c r="N32" s="175" t="s">
         <v>169</v>
       </c>
-      <c r="M28" s="47"/>
-      <c r="N28" s="46"/>
-      <c r="O28" s="47"/>
-    </row>
-    <row r="29" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="G29" s="50"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="51"/>
-      <c r="K29" s="51"/>
-      <c r="L29" s="51"/>
-      <c r="M29" s="52"/>
-      <c r="N29" s="46"/>
-      <c r="O29" s="47"/>
-    </row>
-    <row r="30" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="G30" s="188" t="s">
+      <c r="O32" s="176"/>
+    </row>
+    <row r="33" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G33" s="45" t="s">
         <v>170</v>
       </c>
-      <c r="H30" s="189"/>
-      <c r="I30" s="189"/>
-      <c r="J30" s="189"/>
-      <c r="K30" s="189"/>
-      <c r="L30" s="189"/>
-      <c r="M30" s="190"/>
-      <c r="N30" s="46"/>
-      <c r="O30" s="47"/>
-    </row>
-    <row r="31" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="G31" s="46"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="49"/>
-      <c r="K31" s="49"/>
-      <c r="L31" s="49"/>
-      <c r="M31" s="47"/>
-      <c r="N31" s="46"/>
-      <c r="O31" s="47"/>
-    </row>
-    <row r="32" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="G32" s="46" t="s">
-        <v>171</v>
-      </c>
-      <c r="H32" s="49"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="49" t="s">
-        <v>172</v>
-      </c>
-      <c r="L32" s="53">
-        <v>45600</v>
-      </c>
-      <c r="M32" s="47"/>
-      <c r="N32" s="178" t="s">
-        <v>173</v>
-      </c>
-      <c r="O32" s="179"/>
-    </row>
-    <row r="33" spans="7:15" x14ac:dyDescent="0.3">
-      <c r="G33" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="H33" s="54" t="str">
+      <c r="H33" s="53" t="str">
         <f>PRORRATEO!E30</f>
         <v>Nelida</v>
       </c>
-      <c r="I33" s="49"/>
-      <c r="J33" s="49"/>
-      <c r="K33" s="49"/>
-      <c r="L33" s="49"/>
-      <c r="M33" s="47"/>
-      <c r="N33" s="46"/>
-      <c r="O33" s="47"/>
-    </row>
-    <row r="34" spans="7:15" x14ac:dyDescent="0.3">
-      <c r="G34" s="46"/>
-      <c r="H34" s="49"/>
-      <c r="I34" s="49"/>
-      <c r="J34" s="49"/>
-      <c r="K34" s="49"/>
-      <c r="L34" s="49"/>
-      <c r="M34" s="47"/>
-      <c r="N34" s="180"/>
-      <c r="O34" s="179"/>
-    </row>
-    <row r="35" spans="7:15" x14ac:dyDescent="0.3">
-      <c r="G35" s="46"/>
-      <c r="H35" s="49"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="49"/>
-      <c r="K35" s="49"/>
-      <c r="L35" s="49"/>
-      <c r="M35" s="47"/>
-      <c r="N35" s="46"/>
-      <c r="O35" s="47"/>
-    </row>
-    <row r="36" spans="7:15" x14ac:dyDescent="0.3">
-      <c r="G36" s="46"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="49"/>
-      <c r="J36" s="49"/>
-      <c r="K36" s="49"/>
-      <c r="L36" s="49"/>
-      <c r="M36" s="47"/>
-      <c r="N36" s="46"/>
-      <c r="O36" s="47"/>
-    </row>
-    <row r="37" spans="7:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G37" s="46"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="49"/>
-      <c r="J37" s="49"/>
-      <c r="K37" s="49"/>
-      <c r="L37" s="49"/>
-      <c r="M37" s="47"/>
-      <c r="N37" s="55"/>
-      <c r="O37" s="56"/>
-    </row>
-    <row r="38" spans="7:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G38" s="181" t="s">
-        <v>175</v>
-      </c>
-      <c r="H38" s="182"/>
-      <c r="I38" s="182"/>
-      <c r="J38" s="182"/>
-      <c r="K38" s="182"/>
-      <c r="L38" s="183">
+      <c r="I33" s="48"/>
+      <c r="J33" s="48"/>
+      <c r="K33" s="48"/>
+      <c r="L33" s="48"/>
+      <c r="M33" s="46"/>
+      <c r="N33" s="45"/>
+      <c r="O33" s="46"/>
+    </row>
+    <row r="34" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G34" s="45"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="48"/>
+      <c r="J34" s="48"/>
+      <c r="K34" s="48"/>
+      <c r="L34" s="48"/>
+      <c r="M34" s="46"/>
+      <c r="N34" s="177"/>
+      <c r="O34" s="176"/>
+    </row>
+    <row r="35" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G35" s="45"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="48"/>
+      <c r="J35" s="48"/>
+      <c r="K35" s="48"/>
+      <c r="L35" s="48"/>
+      <c r="M35" s="46"/>
+      <c r="N35" s="45"/>
+      <c r="O35" s="46"/>
+    </row>
+    <row r="36" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G36" s="45"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="48"/>
+      <c r="J36" s="48"/>
+      <c r="K36" s="48"/>
+      <c r="L36" s="48"/>
+      <c r="M36" s="46"/>
+      <c r="N36" s="45"/>
+      <c r="O36" s="46"/>
+    </row>
+    <row r="37" spans="7:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G37" s="45"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="46"/>
+      <c r="N37" s="54"/>
+      <c r="O37" s="55"/>
+    </row>
+    <row r="38" spans="7:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G38" s="178" t="s">
+        <v>171</v>
+      </c>
+      <c r="H38" s="179"/>
+      <c r="I38" s="179"/>
+      <c r="J38" s="179"/>
+      <c r="K38" s="179"/>
+      <c r="L38" s="180">
         <f>PRORRATEO!J30</f>
         <v>0</v>
       </c>
-      <c r="M38" s="184"/>
-      <c r="N38" s="57"/>
-      <c r="O38" s="58"/>
+      <c r="M38" s="181"/>
+      <c r="N38" s="56"/>
+      <c r="O38" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="14">

--- a/ALCORTA 146/Julio/Julio.xlsx
+++ b/ALCORTA 146/Julio/Julio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ALCORTA 146\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A26512E-E21D-48B7-BE4B-1B512F5FA763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863C3D4D-2611-46DC-AD88-97F65C88F707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,14 +20,14 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$55</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Recibo '!$E$6:$N$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$126</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$127</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="204">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>Expensas extraor.</t>
-  </si>
-  <si>
-    <t>SUM</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -483,15 +480,6 @@
     <t>Domicilio: Dr. Melo Nº 2958 - 8vo piso (cita previa) Lanus</t>
   </si>
   <si>
-    <t>TOTAL SAC</t>
-  </si>
-  <si>
-    <t>Deducciones</t>
-  </si>
-  <si>
-    <t>SAC</t>
-  </si>
-  <si>
     <t>GASTOS EXTRAORDINARIOS</t>
   </si>
   <si>
@@ -561,12 +549,6 @@
     <t>Mantenimiento ascensores</t>
   </si>
   <si>
-    <t>MAFRE Seguro de vida colectivo retroactivo 2025</t>
-  </si>
-  <si>
-    <t>ES DE CARÁCTER OBLIGATORIO ENVIAR LOS COMPROBANTES DE TRANSFERENCIAS. DE LO CONTRARIO, DEBEN REVISAR EN LA PARTE INFERIOR QUE HAY DEPOSITOS NO IDENTIFICADOS. A PARTIR DE FEBRERO, QUIEN NO INFORME, CORRERA LA SUERTE DE PAGAR IGUALMENTE LOS PUNITORIOS.</t>
-  </si>
-  <si>
     <t>Olga</t>
   </si>
   <si>
@@ -586,9 +568,6 @@
   </si>
   <si>
     <t>MARIA GARCIA CRISTINA</t>
-  </si>
-  <si>
-    <t>EN MAYO ABONO $131.386,79 Y SE LO PSUIMOS A OTRO</t>
   </si>
   <si>
     <t>PERÍODO: JULIO</t>
@@ -645,6 +624,24 @@
   </si>
   <si>
     <t>Deposito en ef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gasto particular 3A : Acuerdo de pago - Abogada Roxana Goldemberg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gasto particular 4C : Envio carta documento - Abogada Roxana Goldemberg </t>
+  </si>
+  <si>
+    <t>Gasto part.</t>
+  </si>
+  <si>
+    <t>ES DE CARÁCTER OBLIGATORIO ENVIAR LOS COMPROBANTES DE TRANSFERENCIAS. DE LO CONTRARIO, DEBEN REVISAR EN LA PARTE INFERIOR QUE HAY DEPOSITOS NO IDENTIFICADOS. LA LINEA GRIS CORRESPONDE A UN PLAN DE PAGO EN VIGENCIA.</t>
+  </si>
+  <si>
+    <t>Reemplazo Sra. Fernanda</t>
+  </si>
+  <si>
+    <t>TOTAL REEMPLAZO</t>
   </si>
 </sst>
 </file>
@@ -659,7 +656,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="d/m"/>
     <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="173" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -803,7 +800,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -868,6 +865,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1463,7 +1466,7 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="199">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1632,8 +1635,21 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="3" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1744,9 +1760,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2112,7 +2125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M126"/>
+  <dimension ref="A1:M127"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.42578125" customWidth="1"/>
@@ -2128,7 +2141,7 @@
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="58"/>
       <c r="B1" s="59" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C1" s="58"/>
       <c r="D1" s="58"/>
@@ -2137,7 +2150,7 @@
     <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="60"/>
       <c r="B2" s="61" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -2146,7 +2159,7 @@
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="64"/>
       <c r="B3" s="65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C3" s="65"/>
       <c r="D3" s="65"/>
@@ -2155,10 +2168,10 @@
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="64"/>
       <c r="B4" s="65" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C4" s="65" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D4" s="65"/>
       <c r="E4" s="66"/>
@@ -2166,7 +2179,7 @@
     <row r="5" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="64"/>
       <c r="B5" s="65" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C5" s="65"/>
       <c r="D5" s="65"/>
@@ -2177,11 +2190,11 @@
         <v>0</v>
       </c>
       <c r="B6" s="68" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C6" s="68"/>
       <c r="D6" s="68" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E6" s="69"/>
     </row>
@@ -2194,7 +2207,7 @@
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="67" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8" s="68"/>
       <c r="C8" s="68"/>
@@ -2244,34 +2257,34 @@
       <c r="E14" s="70"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="147" t="s">
-        <v>191</v>
-      </c>
-      <c r="B15" s="147"/>
-      <c r="C15" s="147"/>
-      <c r="D15" s="147"/>
-      <c r="E15" s="147"/>
+      <c r="A15" s="158" t="s">
+        <v>184</v>
+      </c>
+      <c r="B15" s="158"/>
+      <c r="C15" s="158"/>
+      <c r="D15" s="158"/>
+      <c r="E15" s="158"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="147"/>
-      <c r="B16" s="147"/>
-      <c r="C16" s="147"/>
-      <c r="D16" s="147"/>
-      <c r="E16" s="147"/>
+      <c r="A16" s="158"/>
+      <c r="B16" s="158"/>
+      <c r="C16" s="158"/>
+      <c r="D16" s="158"/>
+      <c r="E16" s="158"/>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="147"/>
-      <c r="B17" s="147"/>
-      <c r="C17" s="147"/>
-      <c r="D17" s="147"/>
-      <c r="E17" s="147"/>
+      <c r="A17" s="158"/>
+      <c r="B17" s="158"/>
+      <c r="C17" s="158"/>
+      <c r="D17" s="158"/>
+      <c r="E17" s="158"/>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="147"/>
-      <c r="B18" s="147"/>
-      <c r="C18" s="147"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="147"/>
+      <c r="A18" s="158"/>
+      <c r="B18" s="158"/>
+      <c r="C18" s="158"/>
+      <c r="D18" s="158"/>
+      <c r="E18" s="158"/>
     </row>
     <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="70"/>
@@ -2295,39 +2308,39 @@
       <c r="E21" s="70"/>
     </row>
     <row r="22" spans="1:5" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="148"/>
-      <c r="B22" s="149"/>
-      <c r="C22" s="149"/>
-      <c r="D22" s="149"/>
-      <c r="E22" s="149"/>
+      <c r="A22" s="159"/>
+      <c r="B22" s="160"/>
+      <c r="C22" s="160"/>
+      <c r="D22" s="160"/>
+      <c r="E22" s="160"/>
     </row>
     <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="149"/>
-      <c r="B23" s="149"/>
-      <c r="C23" s="149"/>
-      <c r="D23" s="149"/>
-      <c r="E23" s="149"/>
+      <c r="A23" s="160"/>
+      <c r="B23" s="160"/>
+      <c r="C23" s="160"/>
+      <c r="D23" s="160"/>
+      <c r="E23" s="160"/>
     </row>
     <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="149"/>
-      <c r="B24" s="149"/>
-      <c r="C24" s="149"/>
-      <c r="D24" s="149"/>
-      <c r="E24" s="149"/>
+      <c r="A24" s="160"/>
+      <c r="B24" s="160"/>
+      <c r="C24" s="160"/>
+      <c r="D24" s="160"/>
+      <c r="E24" s="160"/>
     </row>
     <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="149"/>
-      <c r="B25" s="149"/>
-      <c r="C25" s="149"/>
-      <c r="D25" s="149"/>
-      <c r="E25" s="149"/>
+      <c r="A25" s="160"/>
+      <c r="B25" s="160"/>
+      <c r="C25" s="160"/>
+      <c r="D25" s="160"/>
+      <c r="E25" s="160"/>
     </row>
     <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="149"/>
-      <c r="B26" s="149"/>
-      <c r="C26" s="149"/>
-      <c r="D26" s="149"/>
-      <c r="E26" s="149"/>
+      <c r="A26" s="160"/>
+      <c r="B26" s="160"/>
+      <c r="C26" s="160"/>
+      <c r="D26" s="160"/>
+      <c r="E26" s="160"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="70"/>
@@ -2338,7 +2351,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="71" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="72"/>
       <c r="C28" s="73"/>
@@ -2347,7 +2360,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B29" s="19"/>
       <c r="C29" s="19"/>
@@ -2356,13 +2369,13 @@
     </row>
     <row r="30" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="76" t="s">
-        <v>112</v>
-      </c>
-      <c r="B30" s="188" t="s">
-        <v>192</v>
+        <v>111</v>
+      </c>
+      <c r="B30" s="77" t="s">
+        <v>185</v>
       </c>
       <c r="C30" s="77"/>
-      <c r="D30" s="189">
+      <c r="D30" s="78">
         <v>2462481.7200000002</v>
       </c>
       <c r="E30" s="77"/>
@@ -2370,10 +2383,10 @@
     <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="76"/>
       <c r="B31" s="140" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C31" s="77"/>
-      <c r="D31" s="189">
+      <c r="D31" s="78">
         <v>7810519.0499999998</v>
       </c>
       <c r="E31" s="77"/>
@@ -2381,7 +2394,7 @@
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="76"/>
       <c r="B32" s="77" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C32" s="77"/>
       <c r="D32" s="78">
@@ -2429,56 +2442,54 @@
         <v>9737411</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="77" t="s">
-        <v>153</v>
+        <v>202</v>
       </c>
       <c r="B38" s="77"/>
       <c r="C38" s="77"/>
-      <c r="D38" s="78"/>
+      <c r="D38" s="78">
+        <v>152000</v>
+      </c>
       <c r="E38" s="77"/>
       <c r="G38">
         <v>235611</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="77" t="s">
-        <v>152</v>
-      </c>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="77"/>
       <c r="B39" s="77"/>
       <c r="C39" s="77"/>
       <c r="D39" s="78"/>
       <c r="E39" s="77"/>
       <c r="G39" s="5">
         <f>E37+E41-G38</f>
-        <v>9501800</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="77" t="s">
-        <v>142</v>
-      </c>
+        <v>9653800</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="77"/>
       <c r="B40" s="77"/>
       <c r="C40" s="77"/>
       <c r="D40" s="83"/>
       <c r="E40" s="77"/>
     </row>
-    <row r="41" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="20" t="s">
-        <v>151</v>
+        <v>203</v>
       </c>
       <c r="B41" s="20"/>
       <c r="C41" s="20"/>
       <c r="D41" s="36"/>
       <c r="E41" s="82">
         <f>SUM(D38:D40)</f>
-        <v>0</v>
+        <v>152000</v>
       </c>
       <c r="F41" s="5"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B42" s="19"/>
       <c r="C42" s="19"/>
@@ -2487,31 +2498,31 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="77" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B43" s="77" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C43" s="77"/>
-      <c r="D43" s="189">
+      <c r="D43" s="78">
         <v>30000</v>
       </c>
       <c r="E43" s="85"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="77" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B44" s="77" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C44" s="77"/>
-      <c r="D44" s="189">
+      <c r="D44" s="78">
         <v>123100</v>
       </c>
       <c r="E44" s="85"/>
       <c r="G44" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2523,7 +2534,7 @@
     </row>
     <row r="46" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B46" s="20"/>
       <c r="C46" s="20"/>
@@ -2544,13 +2555,13 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="76" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B48" s="77"/>
       <c r="C48" s="77" t="s">
-        <v>196</v>
-      </c>
-      <c r="D48" s="145">
+        <v>189</v>
+      </c>
+      <c r="D48" s="17">
         <v>28208</v>
       </c>
       <c r="E48" s="24"/>
@@ -2576,7 +2587,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B51" s="37"/>
       <c r="C51" s="37"/>
@@ -2585,28 +2596,28 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="77" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B52" s="77"/>
       <c r="C52" s="77" t="s">
-        <v>199</v>
-      </c>
-      <c r="D52" s="145">
+        <v>192</v>
+      </c>
+      <c r="D52" s="17">
         <v>1147893.6299999999</v>
       </c>
       <c r="E52" s="24"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="77" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B53" s="77" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C53" s="77" t="s">
-        <v>195</v>
-      </c>
-      <c r="D53" s="139">
+        <v>188</v>
+      </c>
+      <c r="D53" s="24">
         <v>110811.68</v>
       </c>
       <c r="E53" s="24"/>
@@ -2617,13 +2628,13 @@
         <v>Sindicatos periodo JULIO</v>
       </c>
       <c r="B54" s="77" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C54" s="77" t="str">
         <f>C53</f>
         <v>Debito 14/07</v>
       </c>
-      <c r="D54" s="145">
+      <c r="D54" s="17">
         <v>196457.31</v>
       </c>
       <c r="E54" s="24"/>
@@ -2634,13 +2645,13 @@
         <v>Sindicatos periodo JULIO</v>
       </c>
       <c r="B55" s="77" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C55" s="77" t="str">
         <f>C54</f>
         <v>Debito 14/07</v>
       </c>
-      <c r="D55" s="145">
+      <c r="D55" s="17">
         <v>12312.41</v>
       </c>
       <c r="E55" s="87"/>
@@ -2666,7 +2677,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B58" s="37"/>
       <c r="C58" s="37"/>
@@ -2675,40 +2686,40 @@
     </row>
     <row r="59" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="77" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B59" s="91"/>
       <c r="C59" s="77"/>
-      <c r="D59" s="145">
+      <c r="D59" s="17">
         <v>477093.49</v>
       </c>
       <c r="E59" s="24"/>
     </row>
     <row r="60" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="77" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B60" s="91"/>
       <c r="C60" s="77"/>
-      <c r="D60" s="145">
+      <c r="D60" s="17">
         <v>486867.96</v>
       </c>
       <c r="E60" s="24"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="91" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B61" s="91"/>
       <c r="C61" s="77"/>
-      <c r="D61" s="145">
+      <c r="D61" s="17">
         <v>59700</v>
       </c>
       <c r="E61" s="17"/>
     </row>
     <row r="62" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="77" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B62" s="92"/>
       <c r="C62" s="93"/>
@@ -2719,51 +2730,51 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="77" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B63" s="77"/>
       <c r="C63" s="93"/>
-      <c r="D63" s="145">
+      <c r="D63" s="17">
         <v>115000</v>
       </c>
       <c r="E63" s="24"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="77" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B64" s="77"/>
       <c r="C64" s="142"/>
-      <c r="D64" s="142">
+      <c r="D64" s="147">
         <v>203720.4</v>
       </c>
       <c r="E64" s="24"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="77" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B65" s="77"/>
-      <c r="C65" s="145"/>
-      <c r="D65" s="145">
+      <c r="C65" s="144"/>
+      <c r="D65" s="17">
         <v>180608.79</v>
       </c>
       <c r="E65" s="24"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="77" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B66" s="77"/>
-      <c r="C66" s="145"/>
-      <c r="D66" s="145">
+      <c r="C66" s="144"/>
+      <c r="D66" s="17">
         <v>5931.42</v>
       </c>
       <c r="E66" s="142"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="77" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B67" s="77"/>
       <c r="C67" s="77"/>
@@ -2791,7 +2802,7 @@
     </row>
     <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
@@ -2800,233 +2811,234 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="77" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B71" s="77"/>
       <c r="C71" s="77"/>
-      <c r="D71" s="145">
+      <c r="D71" s="17">
         <v>49294.58</v>
       </c>
       <c r="E71" s="85"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="77" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="B72" s="77"/>
       <c r="C72" s="77"/>
-      <c r="D72" s="17">
-        <v>52084.53</v>
+      <c r="D72" s="24">
+        <v>2350</v>
       </c>
       <c r="E72" s="24"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="77" t="s">
-        <v>146</v>
-      </c>
+      <c r="A73" s="77"/>
       <c r="B73" s="77"/>
       <c r="C73" s="77"/>
-      <c r="D73" s="139">
-        <v>2350</v>
-      </c>
-      <c r="E73" s="24"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="77"/>
-      <c r="B74" s="77"/>
-      <c r="C74" s="77"/>
-      <c r="D74" s="24"/>
-      <c r="E74" s="17"/>
+      <c r="D73" s="24"/>
+      <c r="E73" s="17"/>
+    </row>
+    <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" s="19"/>
+      <c r="C74" s="19"/>
+      <c r="D74" s="19"/>
+      <c r="E74" s="96">
+        <f>SUM(D71:D73)</f>
+        <v>51644.58</v>
+      </c>
     </row>
     <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B75" s="19"/>
-      <c r="C75" s="19"/>
-      <c r="D75" s="19"/>
-      <c r="E75" s="96">
-        <f>SUM(D71:D74)</f>
-        <v>103729.11</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B76" s="20"/>
-      <c r="C76" s="20"/>
-      <c r="D76" s="12"/>
-      <c r="E76" s="88"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="77" t="s">
-        <v>38</v>
-      </c>
+      <c r="A75" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B75" s="20"/>
+      <c r="C75" s="20"/>
+      <c r="D75" s="12"/>
+      <c r="E75" s="88"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="77" t="s">
+        <v>37</v>
+      </c>
+      <c r="B76" s="77"/>
+      <c r="C76" s="77"/>
+      <c r="D76" s="17">
+        <f>92201.5+29000</f>
+        <v>121201.5</v>
+      </c>
+      <c r="E76" s="97"/>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="76"/>
       <c r="B77" s="77"/>
       <c r="C77" s="77"/>
-      <c r="D77" s="145">
-        <f>92201.5+29000</f>
+      <c r="D77" s="17"/>
+      <c r="E77" s="98"/>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="B78" s="20"/>
+      <c r="C78" s="20"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="88">
+        <f>SUM(D76:D77)</f>
         <v>121201.5</v>
       </c>
-      <c r="E77" s="97"/>
-    </row>
-    <row r="78" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="76"/>
-      <c r="B78" s="77"/>
-      <c r="C78" s="77"/>
-      <c r="D78" s="17"/>
-      <c r="E78" s="98"/>
     </row>
     <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="B79" s="20"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="12"/>
-      <c r="E79" s="88">
-        <f>SUM(D77:D78)</f>
-        <v>121201.5</v>
-      </c>
+      <c r="A79" s="77"/>
+      <c r="B79" s="77"/>
+      <c r="C79" s="77"/>
+      <c r="D79" s="77"/>
+      <c r="E79" s="99"/>
     </row>
     <row r="80" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="77"/>
-      <c r="B80" s="77"/>
-      <c r="C80" s="77"/>
-      <c r="D80" s="77"/>
-      <c r="E80" s="99"/>
+      <c r="A80" s="100" t="s">
+        <v>177</v>
+      </c>
+      <c r="B80" s="100"/>
+      <c r="C80" s="100"/>
+      <c r="D80" s="101"/>
+      <c r="E80" s="102"/>
     </row>
     <row r="81" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="100" t="s">
-        <v>183</v>
-      </c>
-      <c r="B81" s="100"/>
-      <c r="C81" s="100"/>
-      <c r="D81" s="101"/>
-      <c r="E81" s="102"/>
+      <c r="A81" s="103"/>
+      <c r="B81" s="70"/>
+      <c r="C81" s="70"/>
+      <c r="D81" s="70"/>
+      <c r="E81" s="104"/>
+      <c r="F81" s="31"/>
     </row>
     <row r="82" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="103"/>
-      <c r="B82" s="70"/>
-      <c r="C82" s="70"/>
-      <c r="D82" s="70"/>
-      <c r="E82" s="104"/>
+      <c r="A82" s="105" t="s">
+        <v>38</v>
+      </c>
+      <c r="B82" s="106"/>
+      <c r="C82" s="107"/>
+      <c r="D82" s="107"/>
+      <c r="E82" s="108">
+        <f>(SUM(E30:E80))</f>
+        <v>13239962.17</v>
+      </c>
       <c r="F82" s="31"/>
-    </row>
-    <row r="83" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="105" t="s">
-        <v>39</v>
-      </c>
-      <c r="B83" s="106"/>
-      <c r="C83" s="107"/>
-      <c r="D83" s="107"/>
-      <c r="E83" s="108">
-        <f>(SUM(E30:E81))</f>
-        <v>13140046.699999999</v>
-      </c>
-      <c r="F83" s="31"/>
-      <c r="G83" s="31"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G82" s="31"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="70"/>
+      <c r="B83" s="70"/>
+      <c r="C83" s="70"/>
+      <c r="D83" s="70"/>
+      <c r="E83" s="70"/>
+    </row>
+    <row r="84" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="70"/>
       <c r="B84" s="70"/>
       <c r="C84" s="70"/>
       <c r="D84" s="70"/>
       <c r="E84" s="70"/>
-    </row>
-    <row r="85" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="70"/>
-      <c r="B85" s="70"/>
-      <c r="C85" s="70"/>
+      <c r="F84" s="31"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="169" t="s">
+        <v>150</v>
+      </c>
+      <c r="B85" s="170"/>
+      <c r="C85" s="109"/>
       <c r="D85" s="70"/>
       <c r="E85" s="70"/>
-      <c r="F85" s="31"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="158" t="s">
-        <v>154</v>
-      </c>
-      <c r="B86" s="159"/>
-      <c r="C86" s="109"/>
+    </row>
+    <row r="86" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="161"/>
+      <c r="B86" s="162"/>
+      <c r="C86" s="17"/>
       <c r="D86" s="70"/>
       <c r="E86" s="70"/>
     </row>
-    <row r="87" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="150"/>
-      <c r="B87" s="151"/>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="163"/>
+      <c r="B87" s="164"/>
       <c r="C87" s="17"/>
       <c r="D87" s="70"/>
       <c r="E87" s="70"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="152"/>
-      <c r="B88" s="153"/>
-      <c r="C88" s="17"/>
+      <c r="A88" s="165"/>
+      <c r="B88" s="166"/>
+      <c r="C88" s="110"/>
       <c r="D88" s="70"/>
-      <c r="E88" s="70"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="154"/>
-      <c r="B89" s="155"/>
-      <c r="C89" s="110"/>
+      <c r="E88" s="111"/>
+    </row>
+    <row r="89" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" s="168"/>
+      <c r="C89" s="112">
+        <f>SUM(C86:C88)</f>
+        <v>0</v>
+      </c>
       <c r="D89" s="70"/>
-      <c r="E89" s="111"/>
-    </row>
-    <row r="90" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="156" t="s">
-        <v>16</v>
-      </c>
-      <c r="B90" s="157"/>
-      <c r="C90" s="112">
-        <f>SUM(C87:C89)</f>
-        <v>0</v>
-      </c>
+      <c r="E89" s="70"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="70"/>
+      <c r="B90" s="70"/>
+      <c r="C90" s="70"/>
       <c r="D90" s="70"/>
       <c r="E90" s="70"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="70"/>
-      <c r="B91" s="70"/>
-      <c r="C91" s="70"/>
-      <c r="D91" s="70"/>
+      <c r="A91" s="113" t="s">
+        <v>155</v>
+      </c>
+      <c r="B91" s="113"/>
+      <c r="C91" s="114"/>
+      <c r="D91" s="115"/>
       <c r="E91" s="70"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="113" t="s">
-        <v>159</v>
-      </c>
-      <c r="B92" s="113"/>
-      <c r="C92" s="114"/>
-      <c r="D92" s="115"/>
+    <row r="92" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="70"/>
+      <c r="B92" s="70"/>
+      <c r="C92" s="70"/>
+      <c r="D92" s="70"/>
       <c r="E92" s="70"/>
     </row>
     <row r="93" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="70"/>
-      <c r="B93" s="70"/>
+      <c r="A93" s="116" t="s">
+        <v>39</v>
+      </c>
+      <c r="B93" s="117">
+        <f>E82</f>
+        <v>13239962.17</v>
+      </c>
       <c r="C93" s="70"/>
       <c r="D93" s="70"/>
-      <c r="E93" s="70"/>
-    </row>
-    <row r="94" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="116" t="s">
+      <c r="E93" s="111"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="B94" s="117">
-        <f>E83</f>
-        <v>13140046.699999999</v>
+      <c r="B94" s="119">
+        <f>E82-E80</f>
+        <v>13239962.17</v>
       </c>
       <c r="C94" s="70"/>
       <c r="D94" s="70"/>
-      <c r="E94" s="111"/>
+      <c r="E94" s="70"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="118" t="s">
-        <v>41</v>
-      </c>
-      <c r="B95" s="119">
-        <f>E83-E81</f>
-        <v>13140046.699999999</v>
+      <c r="A95" s="120" t="s">
+        <v>152</v>
+      </c>
+      <c r="B95" s="121">
+        <f>C89+C91</f>
+        <v>0</v>
       </c>
       <c r="C95" s="70"/>
       <c r="D95" s="70"/>
@@ -3034,10 +3046,10 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="120" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B96" s="121">
-        <f>C90+C92</f>
+        <f>C89</f>
         <v>0</v>
       </c>
       <c r="C96" s="70"/>
@@ -3046,199 +3058,203 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="120" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B97" s="121">
-        <f>C90</f>
-        <v>0</v>
+        <f>B94+B96</f>
+        <v>13239962.17</v>
       </c>
       <c r="C97" s="70"/>
       <c r="D97" s="70"/>
       <c r="E97" s="70"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="120" t="s">
-        <v>157</v>
-      </c>
-      <c r="B98" s="121">
-        <f>B95+B97</f>
-        <v>13140046.699999999</v>
-      </c>
+      <c r="A98" s="70"/>
+      <c r="B98" s="70"/>
       <c r="C98" s="70"/>
       <c r="D98" s="70"/>
       <c r="E98" s="70"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="70"/>
-      <c r="B99" s="70"/>
-      <c r="C99" s="70"/>
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="160"/>
+      <c r="B99" s="160"/>
+      <c r="C99" s="160"/>
       <c r="D99" s="70"/>
       <c r="E99" s="70"/>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="149"/>
-      <c r="B100" s="149"/>
-      <c r="C100" s="149"/>
+    <row r="100" spans="1:5" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="160"/>
+      <c r="B100" s="160"/>
+      <c r="C100" s="160"/>
       <c r="D100" s="70"/>
       <c r="E100" s="70"/>
     </row>
-    <row r="101" spans="1:5" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="149"/>
-      <c r="B101" s="149"/>
-      <c r="C101" s="149"/>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="70"/>
+      <c r="B101" s="70"/>
+      <c r="C101" s="70"/>
       <c r="D101" s="70"/>
       <c r="E101" s="70"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="70"/>
-      <c r="B102" s="70"/>
-      <c r="C102" s="70"/>
+      <c r="A102" s="122" t="s">
+        <v>168</v>
+      </c>
+      <c r="B102" s="123"/>
+      <c r="C102" s="124"/>
       <c r="D102" s="70"/>
       <c r="E102" s="70"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="122" t="s">
-        <v>172</v>
-      </c>
-      <c r="B103" s="123"/>
-      <c r="C103" s="124"/>
+      <c r="A103" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B103" s="123">
+        <v>535725.97893585078</v>
+      </c>
+      <c r="C103" s="125"/>
       <c r="D103" s="70"/>
       <c r="E103" s="70"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B104" s="123">
-        <v>535725.97893585078</v>
-      </c>
-      <c r="C104" s="125"/>
-      <c r="D104" s="70"/>
+    <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="126" t="s">
+        <v>43</v>
+      </c>
+      <c r="B104" s="127">
+        <f>PRORRATEO!I44</f>
+        <v>6736812.1796480017</v>
+      </c>
+      <c r="C104" s="124"/>
+      <c r="D104" s="111"/>
       <c r="E104" s="70"/>
     </row>
     <row r="105" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="126" t="s">
-        <v>44</v>
+        <v>197</v>
       </c>
       <c r="B105" s="127">
-        <f>PRORRATEO!I44</f>
-        <v>6668198.9696480017</v>
+        <f>B114</f>
+        <v>614971.40413385991</v>
       </c>
       <c r="C105" s="124"/>
       <c r="D105" s="111"/>
       <c r="E105" s="70"/>
     </row>
-    <row r="106" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="126" t="s">
-        <v>204</v>
-      </c>
-      <c r="B106" s="127">
-        <f>B113</f>
-        <v>614971.40413385991</v>
+    <row r="106" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="128" t="s">
+        <v>198</v>
+      </c>
+      <c r="B106" s="141">
+        <v>-111500</v>
       </c>
       <c r="C106" s="124"/>
       <c r="D106" s="111"/>
       <c r="E106" s="70"/>
     </row>
-    <row r="107" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="128" t="s">
-        <v>43</v>
+        <v>199</v>
       </c>
       <c r="B107" s="141">
-        <f>-(B98)</f>
-        <v>-13140046.699999999</v>
+        <f>-73204-17800</f>
+        <v>-91004</v>
       </c>
       <c r="C107" s="124"/>
-      <c r="D107" s="70"/>
+      <c r="D107" s="111"/>
       <c r="E107" s="70"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="129" t="s">
-        <v>16</v>
-      </c>
-      <c r="B108" s="41">
-        <f>SUM(B104:B107)</f>
-        <v>-5321150.3472822867</v>
-      </c>
-      <c r="C108" s="130"/>
-      <c r="D108" s="111"/>
+    <row r="108" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="128" t="s">
+        <v>42</v>
+      </c>
+      <c r="B108" s="141">
+        <f>-(B97)</f>
+        <v>-13239962.17</v>
+      </c>
+      <c r="C108" s="124"/>
+      <c r="D108" s="70"/>
       <c r="E108" s="70"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="70"/>
-      <c r="B109" s="131"/>
+      <c r="A109" s="129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" s="41">
+        <f>SUM(B103:B108)</f>
+        <v>-5554956.6072822874</v>
+      </c>
       <c r="C109" s="130"/>
-      <c r="D109" s="70"/>
+      <c r="D109" s="111"/>
       <c r="E109" s="70"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="70"/>
-      <c r="B110" s="132"/>
+      <c r="B110" s="131"/>
       <c r="C110" s="130"/>
       <c r="D110" s="70"/>
       <c r="E110" s="70"/>
     </row>
-    <row r="111" spans="1:5" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="70"/>
-      <c r="B111" s="131"/>
-      <c r="C111" s="133"/>
-      <c r="D111" s="134"/>
-      <c r="E111" s="134"/>
+      <c r="B111" s="132"/>
+      <c r="C111" s="130"/>
+      <c r="D111" s="70"/>
+      <c r="E111" s="70"/>
     </row>
     <row r="112" spans="1:5" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="135" t="s">
-        <v>45</v>
-      </c>
-      <c r="B112" s="24"/>
+      <c r="A112" s="70"/>
+      <c r="B112" s="131"/>
       <c r="C112" s="133"/>
       <c r="D112" s="134"/>
-      <c r="E112" s="136"/>
-    </row>
-    <row r="113" spans="1:13" s="28" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="77" t="s">
-        <v>42</v>
-      </c>
-      <c r="B113" s="24">
+      <c r="E112" s="134"/>
+    </row>
+    <row r="113" spans="1:13" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="135" t="s">
+        <v>44</v>
+      </c>
+      <c r="B113" s="24"/>
+      <c r="C113" s="133"/>
+      <c r="D113" s="134"/>
+      <c r="E113" s="136"/>
+    </row>
+    <row r="114" spans="1:13" s="28" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="B114" s="24">
         <v>614971.40413385991</v>
       </c>
-      <c r="C113" s="133"/>
-      <c r="D113" s="136"/>
-      <c r="E113" s="136"/>
-    </row>
-    <row r="114" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="77" t="s">
-        <v>35</v>
-      </c>
-      <c r="B114" s="24">
+      <c r="C114" s="133"/>
+      <c r="D114" s="136"/>
+      <c r="E114" s="136"/>
+    </row>
+    <row r="115" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="77" t="s">
+        <v>34</v>
+      </c>
+      <c r="B115" s="24">
         <f>PRORRATEO!I45</f>
         <v>0</v>
       </c>
-      <c r="C114" s="130"/>
-      <c r="D114" s="111"/>
-      <c r="E114" s="70"/>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A115" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="B115" s="40">
+      <c r="C115" s="130"/>
+      <c r="D115" s="111"/>
+      <c r="E115" s="70"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="77" t="s">
+        <v>196</v>
+      </c>
+      <c r="B116" s="40">
         <v>-614971.4</v>
       </c>
-      <c r="C115" s="130"/>
-      <c r="D115" s="70"/>
-      <c r="E115" s="70"/>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="77"/>
-      <c r="B116" s="40"/>
       <c r="C116" s="130"/>
       <c r="D116" s="70"/>
       <c r="E116" s="70"/>
     </row>
-    <row r="117" spans="1:13" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="140"/>
-      <c r="B117" s="139"/>
-      <c r="C117" s="137"/>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" s="77"/>
+      <c r="B117" s="40"/>
+      <c r="C117" s="130"/>
       <c r="D117" s="70"/>
       <c r="E117" s="70"/>
     </row>
@@ -3249,66 +3265,73 @@
       <c r="D118" s="70"/>
       <c r="E118" s="70"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="135" t="s">
-        <v>46</v>
-      </c>
-      <c r="B119" s="41">
-        <f>SUM(B113:B118)</f>
-        <v>4.1338598821312189E-3</v>
-      </c>
-      <c r="C119" s="124"/>
+    <row r="119" spans="1:13" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="140"/>
+      <c r="B119" s="139"/>
+      <c r="C119" s="137"/>
       <c r="D119" s="70"/>
       <c r="E119" s="70"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="70"/>
-      <c r="B120" s="70"/>
-      <c r="C120" s="70"/>
+      <c r="A120" s="135" t="s">
+        <v>45</v>
+      </c>
+      <c r="B120" s="41">
+        <f>SUM(B114:B119)</f>
+        <v>4.1338598821312189E-3</v>
+      </c>
+      <c r="C120" s="124"/>
       <c r="D120" s="70"/>
       <c r="E120" s="70"/>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A122" s="146" t="s">
-        <v>160</v>
-      </c>
-      <c r="B122" s="146"/>
-      <c r="C122" s="146"/>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" s="70"/>
+      <c r="B121" s="70"/>
+      <c r="C121" s="70"/>
+      <c r="D121" s="70"/>
+      <c r="E121" s="70"/>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A123" s="146"/>
-      <c r="B123" s="146"/>
-      <c r="C123" s="146"/>
+      <c r="A123" s="157" t="s">
+        <v>156</v>
+      </c>
+      <c r="B123" s="157"/>
+      <c r="C123" s="157"/>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A124" s="1"/>
-      <c r="B124" s="1"/>
-      <c r="C124" s="23"/>
+      <c r="A124" s="157"/>
+      <c r="B124" s="157"/>
+      <c r="C124" s="157"/>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A125" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="B125" s="32"/>
-      <c r="C125" s="33">
-        <f>SUM(C124:C124)</f>
-        <v>0</v>
-      </c>
+      <c r="A125" s="1"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="23"/>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M126" s="4"/>
+      <c r="A126" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" s="32"/>
+      <c r="C126" s="33">
+        <f>SUM(C125:C125)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M127" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A122:C123"/>
+    <mergeCell ref="A123:C124"/>
     <mergeCell ref="A15:E18"/>
     <mergeCell ref="A22:E26"/>
+    <mergeCell ref="A86:B86"/>
     <mergeCell ref="A87:B87"/>
     <mergeCell ref="A88:B88"/>
     <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A100:C101"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A99:C100"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3333,7 +3356,7 @@
     <col min="10" max="10" width="12.5703125" customWidth="1"/>
     <col min="11" max="11" width="10.5703125" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="5" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="9.85546875" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" customWidth="1"/>
     <col min="15" max="15" width="14.5703125" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
@@ -3395,11 +3418,11 @@
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
-      <c r="N3" s="169">
+      <c r="N3" s="180">
         <f>O2</f>
         <v>7469692</v>
       </c>
-      <c r="O3" s="169"/>
+      <c r="O3" s="180"/>
       <c r="P3" s="5"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3414,85 +3437,85 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
-      <c r="N4" s="168"/>
-      <c r="O4" s="168"/>
+      <c r="N4" s="179"/>
+      <c r="O4" s="179"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="160" t="s">
+      <c r="A5" s="171" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="162" t="s">
+      <c r="B5" s="173" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="164" t="s">
+      <c r="C5" s="175" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="164" t="s">
+      <c r="D5" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="164" t="s">
-        <v>129</v>
-      </c>
-      <c r="F5" s="160" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="160" t="s">
+      <c r="E5" s="175" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="171" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="171" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="160" t="s">
+      <c r="H5" s="171" t="s">
         <v>13</v>
       </c>
       <c r="I5" s="14"/>
-      <c r="J5" s="172" t="s">
-        <v>143</v>
-      </c>
-      <c r="K5" s="170" t="s">
+      <c r="J5" s="183" t="s">
+        <v>142</v>
+      </c>
+      <c r="K5" s="181" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="170" t="s">
-        <v>33</v>
-      </c>
-      <c r="M5" s="170" t="s">
-        <v>15</v>
-      </c>
-      <c r="N5" s="170" t="s">
+      <c r="L5" s="181" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="181" t="s">
+        <v>200</v>
+      </c>
+      <c r="N5" s="181" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" s="181" t="s">
         <v>31</v>
       </c>
-      <c r="O5" s="170" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="161"/>
-      <c r="B6" s="163"/>
-      <c r="C6" s="165"/>
-      <c r="D6" s="165"/>
-      <c r="E6" s="166"/>
-      <c r="F6" s="161"/>
-      <c r="G6" s="161"/>
-      <c r="H6" s="161"/>
+      <c r="A6" s="172"/>
+      <c r="B6" s="174"/>
+      <c r="C6" s="176"/>
+      <c r="D6" s="176"/>
+      <c r="E6" s="177"/>
+      <c r="F6" s="172"/>
+      <c r="G6" s="172"/>
+      <c r="H6" s="172"/>
       <c r="I6" s="15"/>
-      <c r="J6" s="173"/>
-      <c r="K6" s="171"/>
-      <c r="L6" s="174"/>
-      <c r="M6" s="174"/>
-      <c r="N6" s="174"/>
-      <c r="O6" s="171"/>
+      <c r="J6" s="184"/>
+      <c r="K6" s="182"/>
+      <c r="L6" s="185"/>
+      <c r="M6" s="185"/>
+      <c r="N6" s="185"/>
+      <c r="O6" s="182"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E7" s="34"/>
       <c r="F7" s="1">
@@ -3506,7 +3529,7 @@
         <v>196453.05120000002</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J7" s="7">
         <f>H7-G7</f>
@@ -3532,17 +3555,17 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F8" s="1">
         <v>3.33</v>
@@ -3554,7 +3577,7 @@
         <v>248741</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J8" s="7">
         <f t="shared" ref="J8:J42" si="0">H8-G8</f>
@@ -3581,14 +3604,14 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E9" s="34"/>
       <c r="F9" s="1">
@@ -3601,7 +3624,7 @@
         <v>248000</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J9" s="7">
         <f t="shared" si="0"/>
@@ -3627,14 +3650,14 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E10" s="34"/>
       <c r="F10" s="1">
@@ -3648,7 +3671,7 @@
         <v>255500</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J10" s="7">
         <f t="shared" si="0"/>
@@ -3674,14 +3697,14 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E11" s="34"/>
       <c r="F11" s="1">
@@ -3695,7 +3718,7 @@
         <v>249487.71279999998</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J11" s="7">
         <f t="shared" si="0"/>
@@ -3721,14 +3744,14 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E12" s="34"/>
       <c r="F12" s="1">
@@ -3742,7 +3765,7 @@
         <v>248740.74360000002</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J12" s="7">
         <f t="shared" si="0"/>
@@ -3768,14 +3791,14 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E13" s="34"/>
       <c r="F13" s="1">
@@ -3789,7 +3812,7 @@
         <v>247993.77439999999</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J13" s="7">
         <f t="shared" si="0"/>
@@ -3815,14 +3838,14 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E14" s="34"/>
       <c r="F14" s="1">
@@ -3836,7 +3859,7 @@
         <v>248740.74360000002</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J14" s="7">
         <f t="shared" si="0"/>
@@ -3862,17 +3885,17 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="34" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F15" s="1">
         <v>3.24</v>
@@ -3884,7 +3907,7 @@
         <v>242000</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J15" s="7">
         <f t="shared" si="0"/>
@@ -3908,65 +3931,70 @@
         <v>359833.78375380527</v>
       </c>
       <c r="R15" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="1"/>
-      <c r="C16" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="E16" s="34" t="s">
-        <v>134</v>
-      </c>
-      <c r="F16" s="1">
+      <c r="C16" s="148" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="148" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="148" t="s">
+        <v>133</v>
+      </c>
+      <c r="F16" s="149">
         <v>3.33</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="150">
         <v>665563.98325319996</v>
       </c>
-      <c r="H16" s="29"/>
-      <c r="I16" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="J16" s="7">
+      <c r="H16" s="151">
+        <v>200000</v>
+      </c>
+      <c r="I16" s="151" t="s">
+        <v>121</v>
+      </c>
+      <c r="J16" s="152">
         <f t="shared" si="0"/>
-        <v>-665563.98325319996</v>
-      </c>
-      <c r="K16" s="39">
+        <v>-465563.98325319996</v>
+      </c>
+      <c r="K16" s="153">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L16" s="6">
-        <f t="shared" si="2"/>
+      <c r="L16" s="154">
+        <f>N$3*F16%</f>
         <v>248740.74360000002</v>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23">
+      <c r="M16" s="155">
+        <v>111500</v>
+      </c>
+      <c r="N16" s="156">
         <f>L16+K16-J16+M16</f>
-        <v>914304.7268532</v>
-      </c>
-      <c r="O16" s="23">
+        <v>825804.7268532</v>
+      </c>
+      <c r="O16" s="156">
         <f t="shared" si="3"/>
-        <v>969163.01046439202</v>
-      </c>
+        <v>875353.01046439202</v>
+      </c>
+      <c r="P16" s="11"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E17" s="34"/>
       <c r="F17" s="1">
@@ -3979,7 +4007,7 @@
         <v>257162.35</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J17" s="7">
         <f t="shared" si="0"/>
@@ -4005,14 +4033,14 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="34" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D18" s="34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E18" s="34"/>
       <c r="F18" s="1">
@@ -4025,7 +4053,7 @@
         <v>22605.19</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J18" s="7">
         <f t="shared" si="0"/>
@@ -4051,14 +4079,14 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D19" s="34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E19" s="34"/>
       <c r="F19" s="1">
@@ -4072,7 +4100,7 @@
         <v>242497.05120000002</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J19" s="7">
         <f t="shared" si="0"/>
@@ -4098,17 +4126,17 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D20" s="34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E20" s="34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F20" s="1">
         <v>3.33</v>
@@ -4120,7 +4148,7 @@
         <v>249000</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J20" s="7">
         <f t="shared" si="0"/>
@@ -4146,14 +4174,14 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E21" s="34"/>
       <c r="F21" s="1">
@@ -4164,7 +4192,7 @@
       </c>
       <c r="H21" s="29"/>
       <c r="I21" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J21" s="7">
         <f>H21-G21</f>
@@ -4190,14 +4218,14 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D22" s="34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E22" s="34"/>
       <c r="F22" s="1">
@@ -4208,7 +4236,7 @@
       </c>
       <c r="H22" s="29"/>
       <c r="I22" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J22" s="42">
         <f t="shared" si="0"/>
@@ -4222,30 +4250,32 @@
         <f t="shared" si="2"/>
         <v>248740.74360000002</v>
       </c>
-      <c r="M22" s="23"/>
+      <c r="M22" s="6">
+        <v>91004</v>
+      </c>
       <c r="N22" s="23">
         <f t="shared" si="4"/>
-        <v>2514626.7121669492</v>
+        <v>2605630.7121669492</v>
       </c>
       <c r="O22" s="23">
         <f t="shared" si="3"/>
-        <v>2665504.3148969663</v>
+        <v>2761968.5548969661</v>
       </c>
       <c r="R22" s="30"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E23" s="34" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F23" s="1">
         <v>3.24</v>
@@ -4258,7 +4288,7 @@
         <v>256539.10204800003</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J23" s="7">
         <f t="shared" si="0"/>
@@ -4284,14 +4314,14 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E24" s="34"/>
       <c r="F24" s="1">
@@ -4304,7 +4334,7 @@
         <v>257000</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J24" s="7">
         <f t="shared" si="0"/>
@@ -4330,17 +4360,17 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="34" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D25" s="34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E25" s="34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F25" s="1">
         <v>3.32</v>
@@ -4353,7 +4383,7 @@
         <v>247997.05120000002</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J25" s="7">
         <f t="shared" si="0"/>
@@ -4379,17 +4409,17 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D26" s="34" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E26" s="34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F26" s="1">
         <v>3.33</v>
@@ -4401,7 +4431,7 @@
         <v>248740</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J26" s="7">
         <f t="shared" si="0"/>
@@ -4427,17 +4457,17 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D27" s="34" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E27" s="34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F27" s="1">
         <v>3.24</v>
@@ -4450,7 +4480,7 @@
         <v>242018.02080000003</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J27" s="7">
         <f t="shared" si="0"/>
@@ -4476,14 +4506,14 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D28" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E28" s="34"/>
       <c r="F28" s="1">
@@ -4497,7 +4527,7 @@
         <v>248741.1024</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J28" s="7">
         <f t="shared" si="0"/>
@@ -4523,17 +4553,17 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E29" s="34" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F29" s="1">
         <v>3.32</v>
@@ -4546,7 +4576,7 @@
         <v>532178.5</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J29" s="7">
         <f t="shared" si="0"/>
@@ -4569,23 +4599,23 @@
         <f t="shared" si="3"/>
         <v>262873.40140714392</v>
       </c>
-      <c r="Q29" s="144" t="s">
-        <v>185</v>
+      <c r="Q29" s="146" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="34" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D30" s="34" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E30" s="34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F30" s="1">
         <v>3.33</v>
@@ -4598,7 +4628,7 @@
         <v>248740.74360000002</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J30" s="7">
         <f t="shared" si="0"/>
@@ -4621,23 +4651,21 @@
         <f t="shared" si="3"/>
         <v>263665.18821600004</v>
       </c>
-      <c r="Q30" s="144" t="s">
-        <v>186</v>
-      </c>
+      <c r="Q30" s="146"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D31" s="143" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="E31" s="34" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F31" s="1">
         <v>3.24</v>
@@ -4649,7 +4677,7 @@
         <v>242018</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J31" s="7">
         <f t="shared" si="0"/>
@@ -4675,14 +4703,14 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D32" s="34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E32" s="34"/>
       <c r="F32" s="1">
@@ -4696,7 +4724,7 @@
         <v>122502.94879999998</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J32" s="7">
         <f t="shared" si="0"/>
@@ -4722,14 +4750,14 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E33" s="34"/>
       <c r="F33" s="1">
@@ -4743,7 +4771,7 @@
         <v>122502.94879999998</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J33" s="7">
         <f t="shared" si="0"/>
@@ -4769,14 +4797,14 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D34" s="34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E34" s="34"/>
       <c r="F34" s="1">
@@ -4789,7 +4817,7 @@
         <v>65000</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J34" s="7">
         <f t="shared" si="0"/>
@@ -4815,14 +4843,14 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D35" s="34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E35" s="34"/>
       <c r="F35" s="1">
@@ -4833,7 +4861,7 @@
       </c>
       <c r="H35" s="29"/>
       <c r="I35" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J35" s="7">
         <f t="shared" si="0"/>
@@ -4857,19 +4885,19 @@
         <v>408509.48274328798</v>
       </c>
       <c r="Q35" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D36" s="34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E36" s="34"/>
       <c r="F36" s="1">
@@ -4883,7 +4911,7 @@
         <v>122502.94879999998</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J36" s="7">
         <f t="shared" si="0"/>
@@ -4909,14 +4937,14 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D37" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E37" s="34"/>
       <c r="F37" s="1">
@@ -4930,7 +4958,7 @@
         <v>122502.94879999998</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J37" s="7">
         <f t="shared" si="0"/>
@@ -4956,25 +4984,25 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D38" s="34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E38" s="34"/>
       <c r="F38" s="1">
         <v>1.64</v>
       </c>
-      <c r="G38" s="190">
+      <c r="G38" s="145">
         <v>1115931.8338287675</v>
       </c>
       <c r="H38" s="29"/>
       <c r="I38" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J38" s="7">
         <f t="shared" si="0"/>
@@ -5000,14 +5028,14 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E39" s="34"/>
       <c r="F39" s="1">
@@ -5021,7 +5049,7 @@
         <v>122502.94879999998</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J39" s="7">
         <f t="shared" si="0"/>
@@ -5047,17 +5075,17 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D40" s="34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E40" s="34" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F40" s="1">
         <v>1.64</v>
@@ -5070,7 +5098,7 @@
         <v>122502.94879999998</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J40" s="7">
         <f t="shared" si="0"/>
@@ -5096,14 +5124,14 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D41" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E41" s="34"/>
       <c r="F41" s="1">
@@ -5117,7 +5145,7 @@
         <v>125287.14</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J41" s="7">
         <f>H41-G41</f>
@@ -5143,14 +5171,14 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D42" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E42" s="34"/>
       <c r="F42" s="1">
@@ -5160,14 +5188,15 @@
         <v>276979.24483898393</v>
       </c>
       <c r="H42" s="29">
-        <v>262000</v>
+        <f>262000-131386.79</f>
+        <v>130613.20999999999</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J42" s="7">
         <f t="shared" si="0"/>
-        <v>-14979.244838983926</v>
+        <v>-146366.03483898393</v>
       </c>
       <c r="K42" s="39">
         <f t="shared" si="1"/>
@@ -5180,11 +5209,11 @@
       <c r="M42" s="23"/>
       <c r="N42" s="23">
         <f t="shared" si="4"/>
-        <v>137482.19363898391</v>
+        <v>268868.98363898392</v>
       </c>
       <c r="O42" s="23">
         <f t="shared" si="3"/>
-        <v>145731.12525732294</v>
+        <v>285001.12265732297</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5203,12 +5232,12 @@
       </c>
       <c r="H43" s="9">
         <f>SUM(H7:H42)</f>
-        <v>6668198.9696480017</v>
+        <v>6736812.1796480017</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="138">
         <f t="shared" ref="J43:O43" si="5">SUM(J7:J42)</f>
-        <v>-6638238.3875685921</v>
+        <v>-6569625.1775685921</v>
       </c>
       <c r="K43" s="9">
         <f t="shared" si="5"/>
@@ -5220,30 +5249,30 @@
       </c>
       <c r="M43" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>202504</v>
       </c>
       <c r="N43" s="10">
         <f t="shared" si="5"/>
-        <v>14114653.110368587</v>
+        <v>14248543.900368586</v>
       </c>
       <c r="O43" s="9">
         <f t="shared" si="5"/>
-        <v>14961532.296990706</v>
+        <v>15103456.534390705</v>
       </c>
     </row>
     <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="G44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I44">
         <f>SUMIF(I7:I42,"b",H7:H42)</f>
-        <v>6668198.9696480017</v>
+        <v>6736812.1796480017</v>
       </c>
       <c r="L44" s="11"/>
     </row>
     <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="G45" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I45">
         <f>SUMIF(I7:I42,"e",H7:H42)</f>
@@ -5252,92 +5281,92 @@
     </row>
     <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="G46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H46" s="35">
         <f>I44+I45</f>
-        <v>6668198.9696480017</v>
+        <v>6736812.1796480017</v>
       </c>
     </row>
     <row r="49" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D49" s="167" t="s">
-        <v>178</v>
-      </c>
-      <c r="E49" s="167"/>
-      <c r="F49" s="167"/>
-      <c r="G49" s="167"/>
-      <c r="H49" s="167"/>
-      <c r="I49" s="167"/>
-      <c r="J49" s="167"/>
-      <c r="K49" s="167"/>
-      <c r="L49" s="167"/>
-      <c r="M49" s="167"/>
-      <c r="N49" s="167"/>
+      <c r="D49" s="178" t="s">
+        <v>201</v>
+      </c>
+      <c r="E49" s="178"/>
+      <c r="F49" s="178"/>
+      <c r="G49" s="178"/>
+      <c r="H49" s="178"/>
+      <c r="I49" s="178"/>
+      <c r="J49" s="178"/>
+      <c r="K49" s="178"/>
+      <c r="L49" s="178"/>
+      <c r="M49" s="178"/>
+      <c r="N49" s="178"/>
     </row>
     <row r="50" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D50" s="167"/>
-      <c r="E50" s="167"/>
-      <c r="F50" s="167"/>
-      <c r="G50" s="167"/>
-      <c r="H50" s="167"/>
-      <c r="I50" s="167"/>
-      <c r="J50" s="167"/>
-      <c r="K50" s="167"/>
-      <c r="L50" s="167"/>
-      <c r="M50" s="167"/>
-      <c r="N50" s="167"/>
+      <c r="D50" s="178"/>
+      <c r="E50" s="178"/>
+      <c r="F50" s="178"/>
+      <c r="G50" s="178"/>
+      <c r="H50" s="178"/>
+      <c r="I50" s="178"/>
+      <c r="J50" s="178"/>
+      <c r="K50" s="178"/>
+      <c r="L50" s="178"/>
+      <c r="M50" s="178"/>
+      <c r="N50" s="178"/>
     </row>
     <row r="51" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D51" s="167"/>
-      <c r="E51" s="167"/>
-      <c r="F51" s="167"/>
-      <c r="G51" s="167"/>
-      <c r="H51" s="167"/>
-      <c r="I51" s="167"/>
-      <c r="J51" s="167"/>
-      <c r="K51" s="167"/>
-      <c r="L51" s="167"/>
-      <c r="M51" s="167"/>
-      <c r="N51" s="167"/>
+      <c r="D51" s="178"/>
+      <c r="E51" s="178"/>
+      <c r="F51" s="178"/>
+      <c r="G51" s="178"/>
+      <c r="H51" s="178"/>
+      <c r="I51" s="178"/>
+      <c r="J51" s="178"/>
+      <c r="K51" s="178"/>
+      <c r="L51" s="178"/>
+      <c r="M51" s="178"/>
+      <c r="N51" s="178"/>
     </row>
     <row r="52" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D52" s="167"/>
-      <c r="E52" s="167"/>
-      <c r="F52" s="167"/>
-      <c r="G52" s="167"/>
-      <c r="H52" s="167"/>
-      <c r="I52" s="167"/>
-      <c r="J52" s="167"/>
-      <c r="K52" s="167"/>
-      <c r="L52" s="167"/>
-      <c r="M52" s="167"/>
-      <c r="N52" s="167"/>
+      <c r="D52" s="178"/>
+      <c r="E52" s="178"/>
+      <c r="F52" s="178"/>
+      <c r="G52" s="178"/>
+      <c r="H52" s="178"/>
+      <c r="I52" s="178"/>
+      <c r="J52" s="178"/>
+      <c r="K52" s="178"/>
+      <c r="L52" s="178"/>
+      <c r="M52" s="178"/>
+      <c r="N52" s="178"/>
     </row>
     <row r="53" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D53" s="167"/>
-      <c r="E53" s="167"/>
-      <c r="F53" s="167"/>
-      <c r="G53" s="167"/>
-      <c r="H53" s="167"/>
-      <c r="I53" s="167"/>
-      <c r="J53" s="167"/>
-      <c r="K53" s="167"/>
-      <c r="L53" s="167"/>
-      <c r="M53" s="167"/>
-      <c r="N53" s="167"/>
+      <c r="D53" s="178"/>
+      <c r="E53" s="178"/>
+      <c r="F53" s="178"/>
+      <c r="G53" s="178"/>
+      <c r="H53" s="178"/>
+      <c r="I53" s="178"/>
+      <c r="J53" s="178"/>
+      <c r="K53" s="178"/>
+      <c r="L53" s="178"/>
+      <c r="M53" s="178"/>
+      <c r="N53" s="178"/>
     </row>
     <row r="54" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D54" s="167"/>
-      <c r="E54" s="167"/>
-      <c r="F54" s="167"/>
-      <c r="G54" s="167"/>
-      <c r="H54" s="167"/>
-      <c r="I54" s="167"/>
-      <c r="J54" s="167"/>
-      <c r="K54" s="167"/>
-      <c r="L54" s="167"/>
-      <c r="M54" s="167"/>
-      <c r="N54" s="167"/>
+      <c r="D54" s="178"/>
+      <c r="E54" s="178"/>
+      <c r="F54" s="178"/>
+      <c r="G54" s="178"/>
+      <c r="H54" s="178"/>
+      <c r="I54" s="178"/>
+      <c r="J54" s="178"/>
+      <c r="K54" s="178"/>
+      <c r="L54" s="178"/>
+      <c r="M54" s="178"/>
+      <c r="N54" s="178"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -5371,28 +5400,28 @@
   <sheetData>
     <row r="6" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E7" s="182" t="s">
-        <v>161</v>
-      </c>
-      <c r="F7" s="183"/>
-      <c r="G7" s="183"/>
-      <c r="H7" s="183"/>
-      <c r="I7" s="183"/>
-      <c r="J7" s="183"/>
-      <c r="K7" s="181"/>
+      <c r="E7" s="193" t="s">
+        <v>157</v>
+      </c>
+      <c r="F7" s="194"/>
+      <c r="G7" s="194"/>
+      <c r="H7" s="194"/>
+      <c r="I7" s="194"/>
+      <c r="J7" s="194"/>
+      <c r="K7" s="192"/>
       <c r="L7" s="43"/>
       <c r="M7" s="44"/>
     </row>
     <row r="8" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E8" s="184" t="s">
-        <v>162</v>
-      </c>
-      <c r="F8" s="183"/>
-      <c r="G8" s="183"/>
-      <c r="H8" s="183"/>
-      <c r="I8" s="183"/>
-      <c r="J8" s="183"/>
-      <c r="K8" s="181"/>
+      <c r="E8" s="195" t="s">
+        <v>158</v>
+      </c>
+      <c r="F8" s="194"/>
+      <c r="G8" s="194"/>
+      <c r="H8" s="194"/>
+      <c r="I8" s="194"/>
+      <c r="J8" s="194"/>
+      <c r="K8" s="192"/>
       <c r="L8" s="45"/>
       <c r="M8" s="46"/>
     </row>
@@ -5403,7 +5432,7 @@
       <c r="H9" s="47"/>
       <c r="I9" s="48"/>
       <c r="J9" s="48" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="K9" s="46"/>
       <c r="L9" s="45"/>
@@ -5411,14 +5440,14 @@
     </row>
     <row r="10" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E10" s="45" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F10" s="48"/>
       <c r="G10" s="48"/>
       <c r="H10" s="48"/>
       <c r="I10" s="48"/>
       <c r="J10" s="48" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="K10" s="46"/>
       <c r="L10" s="45"/>
@@ -5436,15 +5465,15 @@
       <c r="M11" s="46"/>
     </row>
     <row r="12" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E12" s="185" t="s">
-        <v>166</v>
-      </c>
-      <c r="F12" s="186"/>
-      <c r="G12" s="186"/>
-      <c r="H12" s="186"/>
-      <c r="I12" s="186"/>
-      <c r="J12" s="186"/>
-      <c r="K12" s="187"/>
+      <c r="E12" s="196" t="s">
+        <v>162</v>
+      </c>
+      <c r="F12" s="197"/>
+      <c r="G12" s="197"/>
+      <c r="H12" s="197"/>
+      <c r="I12" s="197"/>
+      <c r="J12" s="197"/>
+      <c r="K12" s="198"/>
       <c r="L12" s="45"/>
       <c r="M12" s="46"/>
     </row>
@@ -5461,7 +5490,7 @@
     </row>
     <row r="14" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E14" s="45" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F14" s="48"/>
       <c r="G14" s="48" t="str">
@@ -5470,20 +5499,20 @@
       </c>
       <c r="H14" s="48"/>
       <c r="I14" s="48" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J14" s="52">
         <v>45600</v>
       </c>
       <c r="K14" s="46"/>
-      <c r="L14" s="175" t="s">
-        <v>169</v>
-      </c>
-      <c r="M14" s="176"/>
+      <c r="L14" s="186" t="s">
+        <v>165</v>
+      </c>
+      <c r="M14" s="187"/>
     </row>
     <row r="15" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E15" s="45" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F15" s="53" t="str">
         <f>PRORRATEO!C12</f>
@@ -5505,8 +5534,8 @@
       <c r="I16" s="48"/>
       <c r="J16" s="48"/>
       <c r="K16" s="46"/>
-      <c r="L16" s="177"/>
-      <c r="M16" s="176"/>
+      <c r="L16" s="188"/>
+      <c r="M16" s="187"/>
     </row>
     <row r="17" spans="5:15" x14ac:dyDescent="0.25">
       <c r="E17" s="45"/>
@@ -5542,45 +5571,45 @@
       <c r="M19" s="55"/>
     </row>
     <row r="20" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E20" s="178" t="s">
-        <v>171</v>
-      </c>
-      <c r="F20" s="179"/>
-      <c r="G20" s="179"/>
-      <c r="H20" s="179"/>
-      <c r="I20" s="179"/>
-      <c r="J20" s="180">
+      <c r="E20" s="189" t="s">
+        <v>167</v>
+      </c>
+      <c r="F20" s="190"/>
+      <c r="G20" s="190"/>
+      <c r="H20" s="190"/>
+      <c r="I20" s="190"/>
+      <c r="J20" s="191">
         <f>PRORRATEO!H12</f>
         <v>248740.74360000002</v>
       </c>
-      <c r="K20" s="181"/>
+      <c r="K20" s="192"/>
       <c r="L20" s="56"/>
       <c r="M20" s="57"/>
     </row>
     <row r="24" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G25" s="182" t="s">
-        <v>161</v>
-      </c>
-      <c r="H25" s="183"/>
-      <c r="I25" s="183"/>
-      <c r="J25" s="183"/>
-      <c r="K25" s="183"/>
-      <c r="L25" s="183"/>
-      <c r="M25" s="181"/>
+      <c r="G25" s="193" t="s">
+        <v>157</v>
+      </c>
+      <c r="H25" s="194"/>
+      <c r="I25" s="194"/>
+      <c r="J25" s="194"/>
+      <c r="K25" s="194"/>
+      <c r="L25" s="194"/>
+      <c r="M25" s="192"/>
       <c r="N25" s="43"/>
       <c r="O25" s="44"/>
     </row>
     <row r="26" spans="5:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G26" s="184" t="s">
-        <v>162</v>
-      </c>
-      <c r="H26" s="183"/>
-      <c r="I26" s="183"/>
-      <c r="J26" s="183"/>
-      <c r="K26" s="183"/>
-      <c r="L26" s="183"/>
-      <c r="M26" s="181"/>
+      <c r="G26" s="195" t="s">
+        <v>158</v>
+      </c>
+      <c r="H26" s="194"/>
+      <c r="I26" s="194"/>
+      <c r="J26" s="194"/>
+      <c r="K26" s="194"/>
+      <c r="L26" s="194"/>
+      <c r="M26" s="192"/>
       <c r="N26" s="45"/>
       <c r="O26" s="46"/>
     </row>
@@ -5591,7 +5620,7 @@
       <c r="J27" s="47"/>
       <c r="K27" s="48"/>
       <c r="L27" s="48" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="M27" s="46"/>
       <c r="N27" s="45"/>
@@ -5599,14 +5628,14 @@
     </row>
     <row r="28" spans="5:15" x14ac:dyDescent="0.25">
       <c r="G28" s="45" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="H28" s="48"/>
       <c r="I28" s="48"/>
       <c r="J28" s="48"/>
       <c r="K28" s="48"/>
       <c r="L28" s="48" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="M28" s="46"/>
       <c r="N28" s="45"/>
@@ -5624,15 +5653,15 @@
       <c r="O29" s="46"/>
     </row>
     <row r="30" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="G30" s="185" t="s">
-        <v>166</v>
-      </c>
-      <c r="H30" s="186"/>
-      <c r="I30" s="186"/>
-      <c r="J30" s="186"/>
-      <c r="K30" s="186"/>
-      <c r="L30" s="186"/>
-      <c r="M30" s="187"/>
+      <c r="G30" s="196" t="s">
+        <v>162</v>
+      </c>
+      <c r="H30" s="197"/>
+      <c r="I30" s="197"/>
+      <c r="J30" s="197"/>
+      <c r="K30" s="197"/>
+      <c r="L30" s="197"/>
+      <c r="M30" s="198"/>
       <c r="N30" s="45"/>
       <c r="O30" s="46"/>
     </row>
@@ -5649,26 +5678,26 @@
     </row>
     <row r="32" spans="5:15" x14ac:dyDescent="0.25">
       <c r="G32" s="45" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H32" s="48"/>
       <c r="I32" s="48"/>
       <c r="J32" s="48"/>
       <c r="K32" s="48" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="L32" s="52">
         <v>45600</v>
       </c>
       <c r="M32" s="46"/>
-      <c r="N32" s="175" t="s">
-        <v>169</v>
-      </c>
-      <c r="O32" s="176"/>
+      <c r="N32" s="186" t="s">
+        <v>165</v>
+      </c>
+      <c r="O32" s="187"/>
     </row>
     <row r="33" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G33" s="45" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H33" s="53" t="str">
         <f>PRORRATEO!E30</f>
@@ -5690,8 +5719,8 @@
       <c r="K34" s="48"/>
       <c r="L34" s="48"/>
       <c r="M34" s="46"/>
-      <c r="N34" s="177"/>
-      <c r="O34" s="176"/>
+      <c r="N34" s="188"/>
+      <c r="O34" s="187"/>
     </row>
     <row r="35" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G35" s="45"/>
@@ -5727,18 +5756,18 @@
       <c r="O37" s="55"/>
     </row>
     <row r="38" spans="7:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G38" s="178" t="s">
-        <v>171</v>
-      </c>
-      <c r="H38" s="179"/>
-      <c r="I38" s="179"/>
-      <c r="J38" s="179"/>
-      <c r="K38" s="179"/>
-      <c r="L38" s="180">
+      <c r="G38" s="189" t="s">
+        <v>167</v>
+      </c>
+      <c r="H38" s="190"/>
+      <c r="I38" s="190"/>
+      <c r="J38" s="190"/>
+      <c r="K38" s="190"/>
+      <c r="L38" s="191">
         <f>PRORRATEO!J30</f>
         <v>0</v>
       </c>
-      <c r="M38" s="181"/>
+      <c r="M38" s="192"/>
       <c r="N38" s="56"/>
       <c r="O38" s="57"/>
     </row>
